--- a/DevOps_TOC_OCT-2025.xlsx
+++ b/DevOps_TOC_OCT-2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AWS-DevOPS\A-Traning-Vendors\Timesgroup\DevOps\Pre-Post-Test-Feedback\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{227C36CC-BE7C-42A1-9B20-A0D3C8BE556C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2F6A50E-44D5-4D90-8482-CE2CB1CB0560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="378">
   <si>
     <t>Total</t>
   </si>
@@ -3330,12 +3330,625 @@
     <t>Day 29–30:
 Began with QA discussions, including an overview of Azure Pipelines. Covered several key points such as Azure Pipeline concepts, comparisons with other pipeline tools, and common use cases. Demonstrated pipeline functionality in detail. Discussed YAML, including its structure and usage. Explained how to create pipelines using GitHub and Azure DevOps. Created a virtual machine in Azure and configured agents with Azure DevOps and GitHub. Successfully executed and completed all pipeline jobs.</t>
   </si>
+  <si>
+    <t>Day 31: Started working with QA by setting things up step by step. Configured a self-hosted Azure agent for Terraform, set up library variables for the service principal, and created a new pipeline to handle Terraform installation, init, plan, and apply stages. Repeated the process with backend configuration, encountered some issues, and resolved them in the code. Documented the complete end-to-end steps for Day 31.</t>
+  </si>
+  <si>
+    <r>
+      <t>4. Remote State Storage:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Store state in Azure Storage,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AWS S3, or </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Terraform Cloud. Demonstrate remote backend setup.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Learning Objectives: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Understand modern version control practices and how to manage code repositories, branching strategies, and collaboration workflows across Azure DevOps, GitLab, and GitHub.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Learning Objectives: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Gain hands-on experience in designing, building, and managing automated CI/CD pipelines in GitLab and Azure DevOps.</t>
+    </r>
+  </si>
+  <si>
+    <t>Day 32 Summary – QA &amp; CI/CD
+Focused on core DevOps pipeline concepts:
+Built structured pipelines for build, test, and packaging
+Learned CI/CD workflows, triggers, approvals, and gated deployments
+Managed variables and secrets using secure methods
+Practiced monitoring pipelines and debugging failures
+Understood branch protection for safe production releases</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Learning Objectives: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Understand YAML fundamentals and how to design build, test, and deploy pipelines using code-based definitions.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4. Handling Feature Branches: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Set up feature-based builds and temporary environments.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">5. Release Pipelines: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Create release definitions for multi-environment deployment (dev → test → prod).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">7. Lab Exercise: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Build a YAML-based CI/CD pipeline with parallel jobs and conditional stages.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">6. Pipeline Notifications: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Send alerts to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Teams</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, Slack, or email on success/failure.</t>
+    </r>
+  </si>
+  <si>
+    <t>Day-33 Summary
+Worked on CI/CD pipeline concepts and implementation.
+Created build pipelines using YAML templates for standardization.
+Configured CI/CD workflows with triggers, approvals, and gated deployments.
+Learned secure handling of variables and secrets using DevOps tools and Key Vault.
+Monitored pipeline executions, analyzed logs, and improved performance.
+Understood branching strategy and enforced deployments using protected branches.</t>
+  </si>
+  <si>
+    <t>Day-34 Update 
+Started the day with QA concepts, then moved into understanding Azure Artifacts in Azure DevOps.
+✔ Learned what Azure Artifacts is and its purpose
+✔ Explored how to create feeds and manage packages
+✔ Understood real use cases in DevOps workflows
+Key Learnings:
+Centralized package management (npm, Python, Maven, NuGet)
+Secure sharing across teams
+Version control for dependencies
+Advantages:
+Private &amp; secure package storage
+Easy integration with CI/CD
+Supports multiple package types
+Disadvantages:
+Storage cost (billing per GB)
+Requires proper access/token management
+Billing Insight:
+Free tier available
+After limit, charged per GB stored (approx based on usage)
+Hands-On Practice 💻
+Built a Python package
+Generated artifacts (build)
+Pushed to Azure Artifacts feed
+Installed (downloaded) package from feed
+Tested end-to-end workflow
+Also explored:
+Upload &amp; download process
+Feed configuration
+Real DevOps usage scenarios
+👉 Key Takeaway:
+Azure Artifacts is not just storage—it’s essential for dependency management + DevOps maturity</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4. IaC Execution Triggers: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Use GitLab CI/CD or Azure pipelines to trigger IaC runs on commit or tag.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Learning Objectives: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Learn to manage packages and implement manual and automated testing through Azure Artifacts and Test Plans.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create feeds for hosting </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>NuGet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, npm, and Maven packages.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Integrate Login VSI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> or Selenium for load testing.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. PowerShell Integration: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Execute PowerShell scripts to automate post-deployment configuration.</t>
+    </r>
+  </si>
+  <si>
+    <t>Day 35: Focused on QA and Azure DevOps integration. Covered practical examples including Azure DevOps with Maven, Selenium automation, and Windows PowerShell scripts. Conducted live demos for better understanding.
+All code samples and step-by-step documentation have been shared with the team and organized in the Day 35 folder on GitHub.</t>
+  </si>
+  <si>
+    <t>Day-36- Started with QA – Module 13, focusing on Azure DevOps including Pipelines and Repos, along with Terraform, Packer, and Ansible.
+Covered what Packer is, its architecture, and how it fits into the DevOps lifecycle. Also explored Ansible fundamentals, its purpose, advantages, and real-world use cases in a DevOps environment.
+Conducted quick demos on agent configuration for Terraform, Packer, Azure DevOps, and Ansible. Additionally, demonstrated Packer usage for DevOps workflows, including Windows image creation.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Learning Objectives: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Integrate Terraform, PowerShell, and Key Vault into CI/CD pipelines for infrastructure automation.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. Key Vault Integration: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Retrieve secrets securely during build or deploy stages.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Learning Objectives:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Automate golden image creation using modern configuration tools and image version control in Azure.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Image Creation Tools: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Use Packer with Chocolatey and Ansible for Windows base image preparation.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. PowerShell Script Execution: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Run defensive scripts during image build to enforce security settings.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. OS Hardening: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Apply security baselines and compliance settings.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4. Azure Compute Gallery: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Save, manage, and version images in Azure Compute Gallery.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">5. Lab Exercise: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Build and publish an image with Office and Chrome pre-installed.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Image Preparation (Packer + Ansible): </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Create and generalize custom images.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. Azure Compute Gallery: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Save images and manage versions for session host deployment.</t>
+    </r>
+  </si>
+  <si>
+    <t>Day 37–38: End-to-End AVD Automation &amp; Image Lifecycle
+🔷 End-to-End Architecture Overview
+Complete AVD automation flow
+Image lifecycle management approach
+CI/CD driven infrastructure provisioning
+Integration between Packer, Terraform, and Azure DevOps
+🔷 Azure DevOps Pipeline Setup
+Designing multi-stage pipelines for infra + image workflows
+Service connections and authentication
+Pipeline structure for:
+Image build (Packer)
+Infrastructure deployment (Terraform)
+Environment-based pipeline strategy (Dev / QA / Prod)
+🔷 Terraform: Core Infrastructure Setup
+Create Resource Group
+Virtual Network and Subnet design
+Modular Terraform structure for reusability
+Remote state configuration and backend setup
+🔷 Image Preparation using Packer
+Building Windows images using Packer
+Azure builder configuration
+Image generalization (Sysprep)
+Integration with Azure Compute Gallery
+🔷 Provisioning with Ansible &amp; PowerShell
+Using Ansible for configuration management on Windows
+Executing PowerShell scripts for:
+Application installation
+AVD agent prerequisites
+System configuration and hardening
+Combining Packer + Ansible + PowerShell workflows
+🔷 Azure Compute Gallery (ACG)
+Creating and managing image galleries
+Defining image definitions and versions
+Versioning strategy for enterprise environments
+Replication across regions
+🔷 Terraform: Virtual Machine Deployment
+Deploy VMs using custom images from ACG
+Network interface and disk configuration
+Secure credential handling
+Scaling session hosts
+🔷 Demo Workflow 1: Image Build Pipeline
+Trigger Packer build via Azure DevOps
+Run Ansible + PowerShell provisioning
+Publish image to Azure Compute Gallery
+Validate image version creation
+🔷 Demo Workflow 2: Infrastructure Deployment
+Trigger Terraform pipeline
+Deploy:
+Resource Group
+VNet &amp; Subnet
+Virtual Machines (Session Hosts)
+Use latest image version dynamically
+🔷 AVD Deployment using Terraform
+Host Pool creation
+Registration token management
+Session host provisioning and registration
+Scaling and load balancing setup
+🔷 Workspace &amp; Application Groups
+Create Workspace
+Create Desktop Application Group
+Create Remote Application Group
+Publish applications (RemoteApp)
+Assign users/groups (RBAC)
+🔷 End-to-End Integration Flow
+Image → Gallery → Terraform → AVD → User Access
+CI/CD orchestration across pipelines
+Automation triggers and dependencies
+🔷 Best Practices &amp; Enterprise Considerations
+Image versioning and rollback strategy
+Secure secrets management (Key Vault)
+Cost optimization for AVD workloads
+Monitoring and logging integration
+🔷 Final Demo (Complete Flow)
+Build image using Packer pipeline
+Publish to Azure Compute Gallery
+Deploy infrastructure via Terraform
+Create AVD Host Pool &amp; Session Hosts
+Assign applications and users
+Validate end-user access</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. Deploy Host Pools &amp; Session Hosts: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Automate AVD deployment using Terraform or ARM.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4. Workspace and Application Groups: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Create and assign remote applications and desktops.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Learning Objectives: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Deploy, configure, and automate Azure Virtual Desktop environments using Infrastructure as Code</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3418,6 +4031,14 @@
       <sz val="10"/>
       <color rgb="FF00B050"/>
       <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="21">
@@ -3554,7 +4175,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3605,26 +4226,23 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -3662,14 +4280,20 @@
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3975,7 +4599,7 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="16" customHeight="1">
-      <c r="A2" s="27">
+      <c r="A2" s="26">
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
@@ -3989,267 +4613,267 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="16" customHeight="1">
-      <c r="A3" s="27"/>
+      <c r="A3" s="26"/>
       <c r="B3" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18" t="s">
+      <c r="D3" s="20"/>
+      <c r="E3" s="20" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="16" customHeight="1">
-      <c r="A4" s="27"/>
+      <c r="A4" s="26"/>
       <c r="B4" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
     </row>
     <row r="5" spans="1:5" ht="16" customHeight="1">
-      <c r="A5" s="27"/>
+      <c r="A5" s="26"/>
       <c r="B5" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
     </row>
     <row r="6" spans="1:5" ht="16" customHeight="1">
-      <c r="A6" s="27"/>
+      <c r="A6" s="26"/>
       <c r="B6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
     </row>
     <row r="7" spans="1:5" ht="16" customHeight="1">
-      <c r="A7" s="27"/>
+      <c r="A7" s="26"/>
       <c r="B7" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
     </row>
     <row r="8" spans="1:5" ht="16" customHeight="1">
-      <c r="A8" s="27"/>
+      <c r="A8" s="26"/>
       <c r="B8" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
     </row>
     <row r="9" spans="1:5" ht="16" customHeight="1">
-      <c r="A9" s="27"/>
+      <c r="A9" s="26"/>
       <c r="B9" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
     </row>
     <row r="10" spans="1:5" ht="16" customHeight="1">
-      <c r="A10" s="27"/>
+      <c r="A10" s="26"/>
       <c r="B10" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
     </row>
     <row r="11" spans="1:5" ht="16" customHeight="1">
-      <c r="A11" s="27"/>
+      <c r="A11" s="26"/>
       <c r="B11" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
     </row>
     <row r="12" spans="1:5" ht="16" customHeight="1">
-      <c r="A12" s="27"/>
+      <c r="A12" s="26"/>
       <c r="B12" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
     </row>
     <row r="13" spans="1:5" ht="16" customHeight="1">
-      <c r="A13" s="27"/>
+      <c r="A13" s="26"/>
       <c r="B13" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18" t="s">
+      <c r="D13" s="20"/>
+      <c r="E13" s="20" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="16" customHeight="1">
-      <c r="A14" s="27"/>
+      <c r="A14" s="26"/>
       <c r="B14" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
     </row>
     <row r="15" spans="1:5" ht="16" customHeight="1">
-      <c r="A15" s="27"/>
+      <c r="A15" s="26"/>
       <c r="B15" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
     </row>
     <row r="16" spans="1:5" ht="16" customHeight="1">
-      <c r="A16" s="27"/>
+      <c r="A16" s="26"/>
       <c r="B16" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
     </row>
     <row r="17" spans="1:5" ht="16" customHeight="1">
-      <c r="A17" s="27"/>
+      <c r="A17" s="26"/>
       <c r="B17" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
     </row>
     <row r="18" spans="1:5" ht="16" customHeight="1">
-      <c r="A18" s="27"/>
+      <c r="A18" s="26"/>
       <c r="B18" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
     </row>
     <row r="19" spans="1:5" ht="16" customHeight="1">
-      <c r="A19" s="27"/>
+      <c r="A19" s="26"/>
       <c r="B19" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
     </row>
     <row r="20" spans="1:5" ht="16" customHeight="1">
-      <c r="A20" s="27"/>
+      <c r="A20" s="26"/>
       <c r="B20" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
     </row>
     <row r="21" spans="1:5" ht="16" customHeight="1">
-      <c r="A21" s="27"/>
+      <c r="A21" s="26"/>
       <c r="B21" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
     </row>
     <row r="22" spans="1:5" ht="16" customHeight="1">
-      <c r="A22" s="27"/>
+      <c r="A22" s="26"/>
       <c r="B22" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="E22" s="20" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="16" customHeight="1">
-      <c r="A23" s="27"/>
+      <c r="A23" s="26"/>
       <c r="B23" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="19"/>
+      <c r="E23" s="21"/>
     </row>
     <row r="24" spans="1:5" ht="16" customHeight="1">
-      <c r="A24" s="27"/>
+      <c r="A24" s="26"/>
       <c r="B24" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="19"/>
+      <c r="E24" s="21"/>
     </row>
     <row r="25" spans="1:5" ht="16" customHeight="1">
-      <c r="A25" s="27"/>
+      <c r="A25" s="26"/>
       <c r="B25" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E25" s="19"/>
+      <c r="E25" s="21"/>
     </row>
     <row r="26" spans="1:5" ht="16" customHeight="1">
-      <c r="A26" s="27"/>
+      <c r="A26" s="26"/>
       <c r="B26" s="13" t="s">
         <v>270</v>
       </c>
-      <c r="E26" s="19"/>
+      <c r="E26" s="21"/>
     </row>
     <row r="27" spans="1:5" ht="16" customHeight="1">
-      <c r="A27" s="27"/>
+      <c r="A27" s="26"/>
       <c r="B27" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="E27" s="19"/>
+      <c r="E27" s="21"/>
     </row>
     <row r="28" spans="1:5" ht="16" customHeight="1">
-      <c r="A28" s="27"/>
+      <c r="A28" s="26"/>
       <c r="B28" s="13" t="s">
         <v>273</v>
       </c>
-      <c r="E28" s="18" t="s">
+      <c r="E28" s="20" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="16" customHeight="1">
-      <c r="A29" s="27"/>
+      <c r="A29" s="26"/>
       <c r="B29" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="E29" s="19"/>
+      <c r="E29" s="21"/>
     </row>
     <row r="30" spans="1:5" ht="16" customHeight="1">
-      <c r="A30" s="27"/>
+      <c r="A30" s="26"/>
       <c r="B30" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="E30" s="19"/>
+      <c r="E30" s="21"/>
     </row>
     <row r="31" spans="1:5" ht="16" customHeight="1">
-      <c r="A31" s="27"/>
+      <c r="A31" s="26"/>
       <c r="B31" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E31" s="19"/>
+      <c r="E31" s="21"/>
     </row>
     <row r="32" spans="1:5" ht="16" customHeight="1">
-      <c r="A32" s="27"/>
+      <c r="A32" s="26"/>
       <c r="B32" s="14" t="s">
         <v>26</v>
       </c>
       <c r="D32" t="s">
         <v>240</v>
       </c>
-      <c r="E32" s="19"/>
+      <c r="E32" s="21"/>
     </row>
     <row r="33" spans="1:5" ht="16" customHeight="1">
-      <c r="A33" s="27"/>
+      <c r="A33" s="26"/>
       <c r="B33" s="14" t="s">
         <v>158</v>
       </c>
       <c r="D33" t="s">
         <v>241</v>
       </c>
-      <c r="E33" s="19"/>
+      <c r="E33" s="21"/>
     </row>
     <row r="34" spans="1:5" ht="16" customHeight="1">
-      <c r="A34" s="27"/>
+      <c r="A34" s="26"/>
       <c r="B34" s="14" t="s">
         <v>27</v>
       </c>
       <c r="D34" t="s">
         <v>239</v>
       </c>
-      <c r="E34" s="19"/>
+      <c r="E34" s="21"/>
     </row>
     <row r="35" spans="1:5" ht="16" customHeight="1">
-      <c r="A35" s="28">
+      <c r="A35" s="27">
         <v>2</v>
       </c>
       <c r="B35" s="6" t="s">
@@ -4258,113 +4882,113 @@
       <c r="C35" s="8">
         <v>6</v>
       </c>
-      <c r="E35" s="18" t="s">
+      <c r="E35" s="20" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="29">
-      <c r="A36" s="28"/>
+      <c r="A36" s="27"/>
       <c r="B36" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="E36" s="19"/>
+      <c r="E36" s="21"/>
     </row>
     <row r="37" spans="1:5" ht="16" customHeight="1">
-      <c r="A37" s="28"/>
+      <c r="A37" s="27"/>
       <c r="B37" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E37" s="19"/>
+      <c r="E37" s="21"/>
     </row>
     <row r="38" spans="1:5" ht="16" customHeight="1">
-      <c r="A38" s="28"/>
+      <c r="A38" s="27"/>
       <c r="B38" s="13" t="s">
         <v>267</v>
       </c>
-      <c r="E38" s="19"/>
+      <c r="E38" s="21"/>
     </row>
     <row r="39" spans="1:5" ht="16" customHeight="1">
-      <c r="A39" s="28"/>
+      <c r="A39" s="27"/>
       <c r="B39" s="13" t="s">
         <v>268</v>
       </c>
-      <c r="E39" s="19"/>
+      <c r="E39" s="21"/>
     </row>
     <row r="40" spans="1:5" ht="16" customHeight="1">
-      <c r="A40" s="28"/>
+      <c r="A40" s="27"/>
       <c r="B40" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E40" s="18" t="s">
+      <c r="E40" s="20" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="16" customHeight="1">
-      <c r="A41" s="28"/>
+      <c r="A41" s="27"/>
       <c r="B41" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="E41" s="19"/>
+      <c r="E41" s="21"/>
     </row>
     <row r="42" spans="1:5" ht="16" customHeight="1">
-      <c r="A42" s="28"/>
+      <c r="A42" s="27"/>
       <c r="B42" s="14" t="s">
         <v>297</v>
       </c>
-      <c r="E42" s="19"/>
+      <c r="E42" s="21"/>
     </row>
     <row r="43" spans="1:5" ht="16" customHeight="1">
-      <c r="A43" s="28"/>
+      <c r="A43" s="27"/>
       <c r="B43" s="13" t="s">
         <v>294</v>
       </c>
-      <c r="E43" s="19"/>
+      <c r="E43" s="21"/>
     </row>
     <row r="44" spans="1:5" ht="16" customHeight="1">
-      <c r="A44" s="28"/>
+      <c r="A44" s="27"/>
       <c r="B44" s="13" t="s">
         <v>298</v>
       </c>
       <c r="D44" t="s">
         <v>243</v>
       </c>
-      <c r="E44" s="19"/>
+      <c r="E44" s="21"/>
     </row>
     <row r="45" spans="1:5" ht="16" customHeight="1">
-      <c r="A45" s="28"/>
+      <c r="A45" s="27"/>
       <c r="B45" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E45" s="19"/>
+      <c r="E45" s="21"/>
     </row>
     <row r="46" spans="1:5" ht="16" customHeight="1">
-      <c r="A46" s="28"/>
+      <c r="A46" s="27"/>
       <c r="B46" s="14" t="s">
         <v>276</v>
       </c>
-      <c r="E46" s="19"/>
+      <c r="E46" s="21"/>
     </row>
     <row r="47" spans="1:5" ht="16" customHeight="1">
-      <c r="A47" s="28"/>
+      <c r="A47" s="27"/>
       <c r="B47" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E47" s="18" t="s">
+      <c r="E47" s="20" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="29">
-      <c r="A48" s="28"/>
+      <c r="A48" s="27"/>
       <c r="B48" s="13" t="s">
         <v>299</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="E48" s="19"/>
+      <c r="E48" s="21"/>
     </row>
     <row r="49" spans="1:5" ht="16" customHeight="1">
-      <c r="A49" s="29">
+      <c r="A49" s="28">
         <v>3</v>
       </c>
       <c r="B49" s="6" t="s">
@@ -4373,94 +4997,94 @@
       <c r="C49" s="9">
         <v>4</v>
       </c>
-      <c r="E49" s="19"/>
+      <c r="E49" s="21"/>
     </row>
     <row r="50" spans="1:5" ht="16" customHeight="1">
-      <c r="A50" s="29"/>
+      <c r="A50" s="28"/>
       <c r="B50" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="E50" s="19"/>
+      <c r="E50" s="21"/>
     </row>
     <row r="51" spans="1:5" ht="16" customHeight="1">
-      <c r="A51" s="29"/>
+      <c r="A51" s="28"/>
       <c r="B51" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="E51" s="19"/>
+      <c r="E51" s="21"/>
     </row>
     <row r="52" spans="1:5" ht="16" customHeight="1">
-      <c r="A52" s="29"/>
+      <c r="A52" s="28"/>
       <c r="B52" s="13" t="s">
         <v>304</v>
       </c>
-      <c r="E52" s="19"/>
+      <c r="E52" s="21"/>
     </row>
     <row r="53" spans="1:5" ht="16" customHeight="1">
-      <c r="A53" s="29"/>
+      <c r="A53" s="28"/>
       <c r="B53" s="13" t="s">
         <v>305</v>
       </c>
-      <c r="E53" s="18" t="s">
+      <c r="E53" s="20" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="16" customHeight="1">
-      <c r="A54" s="29"/>
+      <c r="A54" s="28"/>
       <c r="B54" s="13" t="s">
         <v>306</v>
       </c>
-      <c r="E54" s="19"/>
+      <c r="E54" s="21"/>
     </row>
     <row r="55" spans="1:5" ht="16" customHeight="1">
-      <c r="A55" s="29"/>
+      <c r="A55" s="28"/>
       <c r="B55" s="13" t="s">
         <v>307</v>
       </c>
-      <c r="E55" s="19"/>
+      <c r="E55" s="21"/>
     </row>
     <row r="56" spans="1:5" ht="16" customHeight="1">
-      <c r="A56" s="29"/>
+      <c r="A56" s="28"/>
       <c r="B56" s="13" t="s">
         <v>308</v>
       </c>
-      <c r="E56" s="19"/>
+      <c r="E56" s="21"/>
     </row>
     <row r="57" spans="1:5" ht="16" customHeight="1">
-      <c r="A57" s="29"/>
+      <c r="A57" s="28"/>
       <c r="B57" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="E57" s="19"/>
+      <c r="E57" s="21"/>
     </row>
     <row r="58" spans="1:5" ht="16" customHeight="1">
-      <c r="A58" s="29"/>
+      <c r="A58" s="28"/>
       <c r="B58" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="E58" s="19"/>
+      <c r="E58" s="21"/>
     </row>
     <row r="59" spans="1:5" ht="16" customHeight="1">
-      <c r="A59" s="29"/>
+      <c r="A59" s="28"/>
       <c r="B59" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="E59" s="18" t="s">
+      <c r="E59" s="20" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="16" customHeight="1">
-      <c r="A60" s="29"/>
+      <c r="A60" s="28"/>
       <c r="B60" s="13" t="s">
         <v>309</v>
       </c>
       <c r="D60" t="s">
         <v>244</v>
       </c>
-      <c r="E60" s="19"/>
+      <c r="E60" s="21"/>
     </row>
     <row r="61" spans="1:5" ht="16" customHeight="1">
-      <c r="A61" s="30">
+      <c r="A61" s="29">
         <v>4</v>
       </c>
       <c r="B61" s="6" t="s">
@@ -4472,68 +5096,68 @@
       <c r="D61" t="s">
         <v>245</v>
       </c>
-      <c r="E61" s="19"/>
+      <c r="E61" s="21"/>
     </row>
     <row r="62" spans="1:5" ht="16" customHeight="1">
-      <c r="A62" s="30"/>
+      <c r="A62" s="29"/>
       <c r="B62" s="12" t="s">
         <v>311</v>
       </c>
-      <c r="E62" s="19"/>
+      <c r="E62" s="21"/>
     </row>
     <row r="63" spans="1:5" ht="16" customHeight="1">
-      <c r="A63" s="30"/>
+      <c r="A63" s="29"/>
       <c r="B63" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="E63" s="19"/>
+      <c r="E63" s="21"/>
     </row>
     <row r="64" spans="1:5" ht="16" customHeight="1">
-      <c r="A64" s="30"/>
+      <c r="A64" s="29"/>
       <c r="B64" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="E64" s="19"/>
+      <c r="E64" s="21"/>
     </row>
     <row r="65" spans="1:5" ht="16" customHeight="1">
-      <c r="A65" s="30"/>
+      <c r="A65" s="29"/>
       <c r="B65" s="13" t="s">
         <v>312</v>
       </c>
-      <c r="E65" s="18" t="s">
+      <c r="E65" s="20" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="16" customHeight="1">
-      <c r="A66" s="30"/>
+      <c r="A66" s="29"/>
       <c r="B66" s="13" t="s">
         <v>313</v>
       </c>
-      <c r="E66" s="19"/>
+      <c r="E66" s="21"/>
     </row>
     <row r="67" spans="1:5" ht="16" customHeight="1">
-      <c r="A67" s="30"/>
+      <c r="A67" s="29"/>
       <c r="B67" s="13" t="s">
         <v>314</v>
       </c>
-      <c r="E67" s="19"/>
+      <c r="E67" s="21"/>
     </row>
     <row r="68" spans="1:5" ht="16" customHeight="1">
-      <c r="A68" s="30"/>
+      <c r="A68" s="29"/>
       <c r="B68" s="13" t="s">
         <v>315</v>
       </c>
-      <c r="E68" s="19"/>
+      <c r="E68" s="21"/>
     </row>
     <row r="69" spans="1:5" ht="16" customHeight="1">
-      <c r="A69" s="30"/>
+      <c r="A69" s="29"/>
       <c r="B69" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="E69" s="19"/>
+      <c r="E69" s="21"/>
     </row>
     <row r="70" spans="1:5" ht="16" customHeight="1">
-      <c r="A70" s="31">
+      <c r="A70" s="30">
         <v>5</v>
       </c>
       <c r="B70" s="6" t="s">
@@ -4542,86 +5166,86 @@
       <c r="C70" s="9">
         <v>4</v>
       </c>
-      <c r="E70" s="18" t="s">
+      <c r="E70" s="20" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="16" customHeight="1">
-      <c r="A71" s="31"/>
+      <c r="A71" s="30"/>
       <c r="B71" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E71" s="19"/>
+      <c r="E71" s="21"/>
     </row>
     <row r="72" spans="1:5" ht="16" customHeight="1">
-      <c r="A72" s="31"/>
+      <c r="A72" s="30"/>
       <c r="B72" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="E72" s="19"/>
+      <c r="E72" s="21"/>
     </row>
     <row r="73" spans="1:5" ht="16" customHeight="1">
-      <c r="A73" s="31"/>
+      <c r="A73" s="30"/>
       <c r="B73" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E73" s="19"/>
+      <c r="E73" s="21"/>
     </row>
     <row r="74" spans="1:5" ht="16" customHeight="1">
-      <c r="A74" s="31"/>
+      <c r="A74" s="30"/>
       <c r="B74" s="13" t="s">
         <v>316</v>
       </c>
-      <c r="E74" s="18" t="s">
+      <c r="E74" s="20" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="16" customHeight="1">
-      <c r="A75" s="31"/>
+      <c r="A75" s="30"/>
       <c r="B75" s="13" t="s">
         <v>317</v>
       </c>
-      <c r="E75" s="19"/>
+      <c r="E75" s="21"/>
     </row>
     <row r="76" spans="1:5" ht="16" customHeight="1">
-      <c r="A76" s="31"/>
+      <c r="A76" s="30"/>
       <c r="B76" s="13" t="s">
         <v>323</v>
       </c>
-      <c r="E76" s="19"/>
+      <c r="E76" s="21"/>
     </row>
     <row r="77" spans="1:5" ht="16" customHeight="1">
-      <c r="A77" s="31"/>
+      <c r="A77" s="30"/>
       <c r="B77" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="E77" s="19"/>
+        <v>346</v>
+      </c>
+      <c r="E77" s="21"/>
     </row>
     <row r="78" spans="1:5" ht="16" customHeight="1">
-      <c r="A78" s="31"/>
+      <c r="A78" s="30"/>
       <c r="B78" s="13" t="s">
         <v>318</v>
       </c>
-      <c r="E78" s="18" t="s">
+      <c r="E78" s="20" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="16" customHeight="1">
-      <c r="A79" s="31"/>
+      <c r="A79" s="30"/>
       <c r="B79" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="E79" s="19"/>
+      <c r="E79" s="21"/>
     </row>
     <row r="80" spans="1:5" ht="16" customHeight="1">
-      <c r="A80" s="31"/>
+      <c r="A80" s="30"/>
       <c r="B80" s="13" t="s">
         <v>324</v>
       </c>
-      <c r="E80" s="19"/>
+      <c r="E80" s="21"/>
     </row>
     <row r="81" spans="1:7" ht="16" customHeight="1">
-      <c r="A81" s="31"/>
+      <c r="A81" s="30"/>
       <c r="B81" s="13" t="s">
         <v>320</v>
       </c>
@@ -4630,16 +5254,16 @@
       </c>
     </row>
     <row r="82" spans="1:7" ht="16" customHeight="1">
-      <c r="A82" s="31"/>
+      <c r="A82" s="30"/>
       <c r="B82" s="13" t="s">
         <v>321</v>
       </c>
-      <c r="E82" s="18" t="s">
+      <c r="E82" s="20" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="16" customHeight="1">
-      <c r="A83" s="32">
+      <c r="A83" s="31">
         <v>6</v>
       </c>
       <c r="B83" s="6" t="s">
@@ -4648,108 +5272,108 @@
       <c r="C83" s="9">
         <v>8</v>
       </c>
-      <c r="E83" s="19"/>
+      <c r="E83" s="21"/>
     </row>
     <row r="84" spans="1:7" ht="16" customHeight="1">
-      <c r="A84" s="32"/>
+      <c r="A84" s="31"/>
       <c r="B84" s="12" t="s">
         <v>336</v>
       </c>
-      <c r="E84" s="19"/>
+      <c r="E84" s="21"/>
     </row>
     <row r="85" spans="1:7" ht="16" customHeight="1">
-      <c r="A85" s="32"/>
+      <c r="A85" s="31"/>
       <c r="B85" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="E85" s="18" t="s">
+      <c r="E85" s="20" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="16" customHeight="1">
-      <c r="A86" s="32"/>
+      <c r="A86" s="31"/>
       <c r="B86" s="13" t="s">
         <v>327</v>
       </c>
-      <c r="E86" s="19"/>
+      <c r="E86" s="21"/>
     </row>
     <row r="87" spans="1:7" ht="16" customHeight="1">
-      <c r="A87" s="32"/>
+      <c r="A87" s="31"/>
       <c r="B87" s="13" t="s">
         <v>328</v>
       </c>
-      <c r="E87" s="19"/>
+      <c r="E87" s="21"/>
     </row>
     <row r="88" spans="1:7" ht="16" customHeight="1">
-      <c r="A88" s="32"/>
+      <c r="A88" s="31"/>
       <c r="B88" s="13" t="s">
         <v>329</v>
       </c>
-      <c r="E88" s="18" t="s">
+      <c r="E88" s="20" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="16" customHeight="1">
-      <c r="A89" s="32"/>
+      <c r="A89" s="31"/>
       <c r="B89" s="13" t="s">
         <v>330</v>
       </c>
-      <c r="E89" s="19"/>
+      <c r="E89" s="21"/>
     </row>
     <row r="90" spans="1:7" ht="16" customHeight="1">
-      <c r="A90" s="32"/>
+      <c r="A90" s="31"/>
       <c r="B90" s="13" t="s">
         <v>331</v>
       </c>
-      <c r="E90" s="19"/>
+      <c r="E90" s="21"/>
     </row>
     <row r="91" spans="1:7" ht="16" customHeight="1">
-      <c r="A91" s="32"/>
+      <c r="A91" s="31"/>
       <c r="B91" s="13" t="s">
         <v>332</v>
       </c>
-      <c r="E91" s="18" t="s">
+      <c r="E91" s="20" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="16" customHeight="1">
-      <c r="A92" s="32"/>
+      <c r="A92" s="31"/>
       <c r="B92" s="13" t="s">
         <v>333</v>
       </c>
-      <c r="E92" s="19"/>
+      <c r="E92" s="21"/>
     </row>
     <row r="93" spans="1:7" ht="16" customHeight="1">
-      <c r="A93" s="32"/>
+      <c r="A93" s="31"/>
       <c r="B93" s="13" t="s">
         <v>337</v>
       </c>
-      <c r="E93" s="19"/>
+      <c r="E93" s="21"/>
     </row>
     <row r="94" spans="1:7" ht="16" customHeight="1">
-      <c r="A94" s="32"/>
+      <c r="A94" s="31"/>
       <c r="B94" s="13" t="s">
         <v>338</v>
       </c>
-      <c r="E94" s="18" t="s">
+      <c r="E94" s="20" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="16" customHeight="1">
-      <c r="A95" s="32"/>
+      <c r="A95" s="31"/>
       <c r="B95" s="13" t="s">
         <v>339</v>
       </c>
       <c r="D95" t="s">
         <v>246</v>
       </c>
-      <c r="E95" s="19"/>
+      <c r="E95" s="21"/>
       <c r="G95" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="16" customHeight="1">
-      <c r="A96" s="33">
+      <c r="A96" s="32">
         <v>7</v>
       </c>
       <c r="B96" s="6" t="s">
@@ -4758,17 +5382,17 @@
       <c r="C96" s="9">
         <v>16</v>
       </c>
-      <c r="E96" s="19"/>
+      <c r="E96" s="21"/>
       <c r="G96" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="33" customHeight="1">
-      <c r="A97" s="33"/>
-      <c r="B97" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E97" s="18" t="s">
+      <c r="A97" s="32"/>
+      <c r="B97" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="E97" s="20" t="s">
         <v>322</v>
       </c>
       <c r="G97" t="s">
@@ -4776,31 +5400,31 @@
       </c>
     </row>
     <row r="98" spans="1:7" ht="16" customHeight="1">
-      <c r="A98" s="33"/>
+      <c r="A98" s="32"/>
       <c r="B98" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E98" s="19"/>
+      <c r="E98" s="21"/>
       <c r="G98" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="16" customHeight="1">
-      <c r="A99" s="33"/>
+      <c r="A99" s="32"/>
       <c r="B99" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E99" s="19"/>
+      <c r="E99" s="21"/>
       <c r="G99" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="16" customHeight="1">
-      <c r="A100" s="33"/>
+      <c r="A100" s="32"/>
       <c r="B100" s="14" t="s">
         <v>340</v>
       </c>
-      <c r="E100" s="18" t="s">
+      <c r="E100" s="20" t="s">
         <v>325</v>
       </c>
       <c r="G100" t="s">
@@ -4808,244 +5432,251 @@
       </c>
     </row>
     <row r="101" spans="1:7" ht="16" customHeight="1">
-      <c r="A101" s="33"/>
+      <c r="A101" s="32"/>
       <c r="B101" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="E101" s="19"/>
+      <c r="E101" s="21"/>
       <c r="G101" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="16" customHeight="1">
-      <c r="A102" s="33"/>
+      <c r="A102" s="32"/>
       <c r="B102" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="E102" s="19"/>
+      <c r="E102" s="21"/>
       <c r="G102" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="16" customHeight="1">
-      <c r="A103" s="33"/>
+      <c r="A103" s="32"/>
       <c r="B103" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E103" s="19"/>
+      <c r="E103" s="21"/>
     </row>
     <row r="104" spans="1:7" ht="16" customHeight="1">
-      <c r="A104" s="33"/>
+      <c r="A104" s="32"/>
       <c r="B104" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E104" s="19" t="s">
+      <c r="E104" s="21" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="16" customHeight="1">
-      <c r="A105" s="33"/>
+      <c r="A105" s="32"/>
       <c r="B105" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="E105" s="19"/>
+      <c r="E105" s="21"/>
     </row>
     <row r="106" spans="1:7" ht="16" customHeight="1">
-      <c r="A106" s="33"/>
+      <c r="A106" s="32"/>
       <c r="B106" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="E106" s="19"/>
+      <c r="E106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="16" customHeight="1">
-      <c r="A107" s="33"/>
+      <c r="A107" s="32"/>
       <c r="B107" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="E107" s="18" t="s">
+      <c r="E107" s="20" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="16" customHeight="1">
-      <c r="A108" s="33"/>
+      <c r="A108" s="32"/>
       <c r="B108" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="E108" s="19"/>
+      <c r="E108" s="21"/>
     </row>
     <row r="109" spans="1:7" ht="16" customHeight="1">
-      <c r="A109" s="33"/>
+      <c r="A109" s="32"/>
       <c r="B109" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="E109" s="19"/>
+      <c r="E109" s="21"/>
     </row>
     <row r="110" spans="1:7" ht="16" customHeight="1">
-      <c r="A110" s="33"/>
+      <c r="A110" s="32"/>
       <c r="B110" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="E110" s="24" t="s">
+      <c r="E110" s="36" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="16" customHeight="1">
-      <c r="A111" s="33"/>
+      <c r="A111" s="32"/>
       <c r="B111" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="E111" s="25"/>
+      <c r="E111" s="24"/>
     </row>
     <row r="112" spans="1:7" ht="16" customHeight="1">
-      <c r="A112" s="33"/>
+      <c r="A112" s="32"/>
       <c r="B112" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="E112" s="25"/>
+      <c r="E112" s="24"/>
     </row>
     <row r="113" spans="1:5" ht="16" customHeight="1">
-      <c r="A113" s="33"/>
+      <c r="A113" s="32"/>
       <c r="B113" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="E113" s="25"/>
+      <c r="E113" s="24"/>
     </row>
     <row r="114" spans="1:5" ht="16" customHeight="1">
-      <c r="A114" s="33"/>
+      <c r="A114" s="32"/>
       <c r="B114" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="E114" s="25" t="s">
+      <c r="E114" s="24" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="16" customHeight="1">
-      <c r="A115" s="33"/>
+      <c r="A115" s="32"/>
       <c r="B115" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="E115" s="25"/>
+      <c r="E115" s="24"/>
     </row>
     <row r="116" spans="1:5" ht="16" customHeight="1">
-      <c r="A116" s="33"/>
+      <c r="A116" s="32"/>
       <c r="B116" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E116" s="25"/>
+      <c r="E116" s="24"/>
     </row>
     <row r="117" spans="1:5" ht="16" customHeight="1">
-      <c r="A117" s="33"/>
+      <c r="A117" s="32"/>
       <c r="B117" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="E117" s="18" t="s">
+      <c r="E117" s="20" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="16" customHeight="1">
-      <c r="A118" s="33"/>
+      <c r="A118" s="32"/>
       <c r="B118" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="E118" s="19"/>
+      <c r="E118" s="21"/>
     </row>
     <row r="119" spans="1:5" ht="16" customHeight="1">
-      <c r="A119" s="33"/>
+      <c r="A119" s="32"/>
       <c r="B119" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="E119" s="19"/>
+      <c r="E119" s="21"/>
     </row>
     <row r="120" spans="1:5" ht="16" customHeight="1">
-      <c r="A120" s="33"/>
+      <c r="A120" s="32"/>
       <c r="B120" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="E120" s="18" t="s">
+      <c r="E120" s="20" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="16" customHeight="1">
-      <c r="A121" s="33"/>
+      <c r="A121" s="32"/>
       <c r="B121" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="E121" s="19"/>
+      <c r="E121" s="21"/>
     </row>
     <row r="122" spans="1:5" ht="16" customHeight="1">
-      <c r="A122" s="33"/>
+      <c r="A122" s="32"/>
       <c r="B122" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="E122" s="19"/>
+      <c r="E122" s="21"/>
     </row>
     <row r="123" spans="1:5" ht="16" customHeight="1">
-      <c r="A123" s="33"/>
+      <c r="A123" s="32"/>
       <c r="B123" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="E123" s="18" t="s">
+      <c r="E123" s="20" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="16" customHeight="1">
-      <c r="A124" s="33"/>
+      <c r="A124" s="32"/>
       <c r="B124" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="E124" s="19"/>
+      <c r="E124" s="21"/>
     </row>
     <row r="125" spans="1:5" ht="16" customHeight="1">
-      <c r="A125" s="33"/>
+      <c r="A125" s="32"/>
       <c r="B125" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E125" s="19"/>
+      <c r="E125" s="21"/>
     </row>
     <row r="126" spans="1:5" ht="16" customHeight="1">
-      <c r="A126" s="33"/>
+      <c r="A126" s="32"/>
       <c r="B126" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="E126" s="39"/>
+      <c r="E126" s="21" t="s">
+        <v>345</v>
+      </c>
     </row>
     <row r="127" spans="1:5" ht="16" customHeight="1">
-      <c r="A127" s="33"/>
+      <c r="A127" s="32"/>
       <c r="B127" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="E127" s="39"/>
+      <c r="E127" s="21"/>
     </row>
     <row r="128" spans="1:5" ht="16" customHeight="1">
-      <c r="A128" s="33"/>
+      <c r="A128" s="32"/>
       <c r="B128" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="E128" s="39"/>
-    </row>
-    <row r="129" spans="1:4" ht="16" customHeight="1">
-      <c r="A129" s="33"/>
+      <c r="E128" s="21"/>
+    </row>
+    <row r="129" spans="1:5" ht="16" customHeight="1">
+      <c r="A129" s="32"/>
       <c r="B129" s="14" t="s">
         <v>71</v>
       </c>
       <c r="D129" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="130" spans="1:4" ht="16" customHeight="1">
-      <c r="A130" s="33"/>
+      <c r="E129" s="20" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" ht="16" customHeight="1">
+      <c r="A130" s="32"/>
       <c r="B130" s="14" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="131" spans="1:4" ht="16" customHeight="1">
-      <c r="A131" s="33"/>
+      <c r="E130" s="21"/>
+    </row>
+    <row r="131" spans="1:5" ht="16" customHeight="1">
+      <c r="A131" s="32"/>
       <c r="B131" s="14" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="132" spans="1:4" ht="16" customHeight="1">
-      <c r="A132" s="34">
+      <c r="E131" s="21"/>
+    </row>
+    <row r="132" spans="1:5" ht="16" customHeight="1">
+      <c r="A132" s="33">
         <v>8</v>
       </c>
       <c r="B132" s="6" t="s">
@@ -5054,126 +5685,152 @@
       <c r="C132" s="9">
         <v>8</v>
       </c>
-    </row>
-    <row r="133" spans="1:4" ht="16" customHeight="1">
-      <c r="A133" s="34"/>
-      <c r="B133" s="3" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" ht="16" customHeight="1">
-      <c r="A134" s="34"/>
-      <c r="B134" s="2" t="s">
+      <c r="E132" s="20" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" ht="16" customHeight="1">
+      <c r="A133" s="33"/>
+      <c r="B133" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="E133" s="21"/>
+    </row>
+    <row r="134" spans="1:5" ht="16" customHeight="1">
+      <c r="A134" s="33"/>
+      <c r="B134" s="18" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="135" spans="1:4" ht="16" customHeight="1">
-      <c r="A135" s="34"/>
-      <c r="B135" s="4" t="s">
+      <c r="E134" s="21"/>
+    </row>
+    <row r="135" spans="1:5" ht="16" customHeight="1">
+      <c r="A135" s="33"/>
+      <c r="B135" s="13" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="136" spans="1:4" ht="16" customHeight="1">
-      <c r="A136" s="34"/>
-      <c r="B136" s="5" t="s">
+      <c r="E135" s="21"/>
+    </row>
+    <row r="136" spans="1:5" ht="16" customHeight="1">
+      <c r="A136" s="33"/>
+      <c r="B136" s="14" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="137" spans="1:4" ht="16" customHeight="1">
-      <c r="A137" s="34"/>
-      <c r="B137" s="5" t="s">
+    <row r="137" spans="1:5" ht="16" customHeight="1">
+      <c r="A137" s="33"/>
+      <c r="B137" s="14" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="138" spans="1:4" ht="16" customHeight="1">
-      <c r="A138" s="34"/>
-      <c r="B138" s="4" t="s">
+    <row r="138" spans="1:5" ht="16" customHeight="1">
+      <c r="A138" s="33"/>
+      <c r="B138" s="13" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="139" spans="1:4" ht="16" customHeight="1">
-      <c r="A139" s="34"/>
-      <c r="B139" s="5" t="s">
+      <c r="E138" s="20" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" ht="16" customHeight="1">
+      <c r="A139" s="33"/>
+      <c r="B139" s="14" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="140" spans="1:4" ht="16" customHeight="1">
-      <c r="A140" s="34"/>
-      <c r="B140" s="5" t="s">
+      <c r="E139" s="21"/>
+    </row>
+    <row r="140" spans="1:5" ht="16" customHeight="1">
+      <c r="A140" s="33"/>
+      <c r="B140" s="14" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="141" spans="1:4" ht="16" customHeight="1">
-      <c r="A141" s="34"/>
-      <c r="B141" s="4" t="s">
+      <c r="E140" s="21"/>
+    </row>
+    <row r="141" spans="1:5" ht="16" customHeight="1">
+      <c r="A141" s="33"/>
+      <c r="B141" s="13" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="142" spans="1:4" ht="16" customHeight="1">
-      <c r="A142" s="34"/>
-      <c r="B142" s="5" t="s">
+      <c r="E141" s="21"/>
+    </row>
+    <row r="142" spans="1:5" ht="16" customHeight="1">
+      <c r="A142" s="33"/>
+      <c r="B142" s="14" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="143" spans="1:4" ht="16" customHeight="1">
-      <c r="A143" s="34"/>
-      <c r="B143" s="5" t="s">
+      <c r="E142" s="21"/>
+    </row>
+    <row r="143" spans="1:5" ht="16" customHeight="1">
+      <c r="A143" s="33"/>
+      <c r="B143" s="14" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="144" spans="1:4" ht="16" customHeight="1">
-      <c r="A144" s="34"/>
-      <c r="B144" s="4" t="s">
+      <c r="E143" s="21"/>
+    </row>
+    <row r="144" spans="1:5" ht="16" customHeight="1">
+      <c r="A144" s="33"/>
+      <c r="B144" s="13" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="145" spans="1:4" ht="16" customHeight="1">
-      <c r="A145" s="34"/>
-      <c r="B145" s="5" t="s">
+      <c r="E144" s="21"/>
+    </row>
+    <row r="145" spans="1:5" ht="16" customHeight="1">
+      <c r="A145" s="33"/>
+      <c r="B145" s="14" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="146" spans="1:4" ht="16" customHeight="1">
-      <c r="A146" s="34"/>
-      <c r="B146" s="5" t="s">
+      <c r="E145" s="21"/>
+    </row>
+    <row r="146" spans="1:5" ht="16" customHeight="1">
+      <c r="A146" s="33"/>
+      <c r="B146" s="14" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="147" spans="1:4" ht="16" customHeight="1">
-      <c r="A147" s="34"/>
-      <c r="B147" s="4" t="s">
+      <c r="E146" s="20" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" ht="16" customHeight="1">
+      <c r="A147" s="33"/>
+      <c r="B147" s="13" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="148" spans="1:4" ht="16" customHeight="1">
-      <c r="A148" s="34"/>
-      <c r="B148" s="5" t="s">
+      <c r="E147" s="21"/>
+    </row>
+    <row r="148" spans="1:5" ht="16" customHeight="1">
+      <c r="A148" s="33"/>
+      <c r="B148" s="14" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="149" spans="1:4" ht="16" customHeight="1">
-      <c r="A149" s="34"/>
+      <c r="E148" s="21"/>
+    </row>
+    <row r="149" spans="1:5" ht="16" customHeight="1">
+      <c r="A149" s="33"/>
       <c r="B149" s="4" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="150" spans="1:4" ht="16" customHeight="1">
-      <c r="A150" s="34"/>
+      <c r="E149" s="21"/>
+    </row>
+    <row r="150" spans="1:5" ht="16" customHeight="1">
+      <c r="A150" s="33"/>
       <c r="B150" s="5" t="s">
         <v>89</v>
       </c>
       <c r="D150" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="151" spans="1:4" ht="16" customHeight="1">
-      <c r="A151" s="34"/>
+      <c r="E150" s="20" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" ht="16" customHeight="1">
+      <c r="A151" s="33"/>
       <c r="B151" s="5" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="152" spans="1:4" ht="16" customHeight="1">
-      <c r="A152" s="35">
+      <c r="E151" s="21"/>
+    </row>
+    <row r="152" spans="1:5" ht="16" customHeight="1">
+      <c r="A152" s="34">
         <v>9</v>
       </c>
       <c r="B152" s="6" t="s">
@@ -5182,99 +5839,117 @@
       <c r="C152" s="9">
         <v>8</v>
       </c>
-    </row>
-    <row r="153" spans="1:4" ht="16" customHeight="1">
-      <c r="A153" s="35"/>
-      <c r="B153" s="3" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" ht="16" customHeight="1">
-      <c r="A154" s="35"/>
+      <c r="E152" s="21"/>
+    </row>
+    <row r="153" spans="1:5" ht="16" customHeight="1">
+      <c r="A153" s="34"/>
+      <c r="B153" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="E153" s="21"/>
+    </row>
+    <row r="154" spans="1:5" ht="16" customHeight="1">
+      <c r="A154" s="34"/>
       <c r="B154" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="155" spans="1:4" ht="16" customHeight="1">
-      <c r="A155" s="35"/>
-      <c r="B155" s="4" t="s">
+      <c r="E154" s="21"/>
+    </row>
+    <row r="155" spans="1:5" ht="16" customHeight="1">
+      <c r="A155" s="34"/>
+      <c r="B155" s="13" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="156" spans="1:4" ht="16" customHeight="1">
-      <c r="A156" s="35"/>
+      <c r="E155" s="21"/>
+    </row>
+    <row r="156" spans="1:5" ht="16" customHeight="1">
+      <c r="A156" s="34"/>
       <c r="B156" s="14" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="157" spans="1:4" ht="16" customHeight="1">
-      <c r="A157" s="35"/>
+      <c r="E156" s="20" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" ht="16" customHeight="1">
+      <c r="A157" s="34"/>
       <c r="B157" s="14" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="158" spans="1:4" ht="16" customHeight="1">
-      <c r="A158" s="35"/>
-      <c r="B158" s="4" t="s">
+      <c r="E157" s="21"/>
+    </row>
+    <row r="158" spans="1:5" ht="16" customHeight="1">
+      <c r="A158" s="34"/>
+      <c r="B158" s="13" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="159" spans="1:4" ht="16" customHeight="1">
-      <c r="A159" s="35"/>
-      <c r="B159" s="5" t="s">
+      <c r="E158" s="21"/>
+    </row>
+    <row r="159" spans="1:5" ht="16" customHeight="1">
+      <c r="A159" s="34"/>
+      <c r="B159" s="14" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="160" spans="1:4" ht="16" customHeight="1">
-      <c r="A160" s="35"/>
-      <c r="B160" s="5" t="s">
+      <c r="E159" s="21"/>
+    </row>
+    <row r="160" spans="1:5" ht="16" customHeight="1">
+      <c r="A160" s="34"/>
+      <c r="B160" s="14" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="161" spans="1:3" ht="16" customHeight="1">
-      <c r="A161" s="35"/>
-      <c r="B161" s="4" t="s">
+      <c r="E160" s="21"/>
+    </row>
+    <row r="161" spans="1:5" ht="16" customHeight="1">
+      <c r="A161" s="34"/>
+      <c r="B161" s="13" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="162" spans="1:3" ht="16" customHeight="1">
-      <c r="A162" s="35"/>
-      <c r="B162" s="5" t="s">
+      <c r="E161" s="21"/>
+    </row>
+    <row r="162" spans="1:5" ht="16" customHeight="1">
+      <c r="A162" s="34"/>
+      <c r="B162" s="14" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="163" spans="1:3" ht="16" customHeight="1">
-      <c r="A163" s="35"/>
+      <c r="E162" s="21"/>
+    </row>
+    <row r="163" spans="1:5" ht="16" customHeight="1">
+      <c r="A163" s="34"/>
       <c r="B163" s="5" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="164" spans="1:3" ht="16" customHeight="1">
-      <c r="A164" s="35"/>
-      <c r="B164" s="4" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" ht="16" customHeight="1">
-      <c r="A165" s="35"/>
-      <c r="B165" s="4" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" ht="16" customHeight="1">
-      <c r="A166" s="35"/>
-      <c r="B166" s="4" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" ht="16" customHeight="1">
-      <c r="A167" s="35"/>
-      <c r="B167" s="4" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" ht="16" customHeight="1">
-      <c r="A168" s="36">
+      <c r="E163" s="21"/>
+    </row>
+    <row r="164" spans="1:5" ht="16" customHeight="1">
+      <c r="A164" s="34"/>
+      <c r="B164" s="13" t="s">
+        <v>351</v>
+      </c>
+      <c r="E164" s="21"/>
+    </row>
+    <row r="165" spans="1:5" ht="16" customHeight="1">
+      <c r="A165" s="34"/>
+      <c r="B165" s="13" t="s">
+        <v>352</v>
+      </c>
+      <c r="E165" s="21"/>
+    </row>
+    <row r="166" spans="1:5" ht="16" customHeight="1">
+      <c r="A166" s="34"/>
+      <c r="B166" s="13" t="s">
+        <v>354</v>
+      </c>
+      <c r="E166" s="21"/>
+    </row>
+    <row r="167" spans="1:5" ht="16" customHeight="1">
+      <c r="A167" s="34"/>
+      <c r="B167" s="13" t="s">
+        <v>353</v>
+      </c>
+      <c r="E167" s="21"/>
+    </row>
+    <row r="168" spans="1:5" ht="16" customHeight="1">
+      <c r="A168" s="35">
         <v>10</v>
       </c>
       <c r="B168" s="6" t="s">
@@ -5284,63 +5959,63 @@
         <v>8</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="16" customHeight="1">
-      <c r="A169" s="36"/>
-      <c r="B169" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" ht="16" customHeight="1">
-      <c r="A170" s="36"/>
-      <c r="B170" s="2" t="s">
+    <row r="169" spans="1:5" ht="16" customHeight="1">
+      <c r="A169" s="35"/>
+      <c r="B169" s="12" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" ht="16" customHeight="1">
+      <c r="A170" s="35"/>
+      <c r="B170" s="18" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="16" customHeight="1">
-      <c r="A171" s="36"/>
-      <c r="B171" s="4" t="s">
+    <row r="171" spans="1:5" ht="16" customHeight="1">
+      <c r="A171" s="35"/>
+      <c r="B171" s="13" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="16" customHeight="1">
-      <c r="A172" s="36"/>
-      <c r="B172" s="5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3" ht="16" customHeight="1">
-      <c r="A173" s="36"/>
-      <c r="B173" s="5" t="s">
+    <row r="172" spans="1:5" ht="16" customHeight="1">
+      <c r="A172" s="35"/>
+      <c r="B172" s="14" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" ht="16" customHeight="1">
+      <c r="A173" s="35"/>
+      <c r="B173" s="14" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="16" customHeight="1">
-      <c r="A174" s="36"/>
-      <c r="B174" s="4" t="s">
+    <row r="174" spans="1:5" ht="16" customHeight="1">
+      <c r="A174" s="35"/>
+      <c r="B174" s="13" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="16" customHeight="1">
-      <c r="A175" s="36"/>
-      <c r="B175" s="5" t="s">
+    <row r="175" spans="1:5" ht="16" customHeight="1">
+      <c r="A175" s="35"/>
+      <c r="B175" s="14" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="16" customHeight="1">
-      <c r="A176" s="36"/>
-      <c r="B176" s="5" t="s">
-        <v>107</v>
+    <row r="176" spans="1:5" ht="16" customHeight="1">
+      <c r="A176" s="35"/>
+      <c r="B176" s="14" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="16" customHeight="1">
-      <c r="A177" s="36"/>
-      <c r="B177" s="4" t="s">
+      <c r="A177" s="35"/>
+      <c r="B177" s="13" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="16" customHeight="1">
-      <c r="A178" s="36"/>
-      <c r="B178" s="5" t="s">
+      <c r="A178" s="35"/>
+      <c r="B178" s="14" t="s">
         <v>109</v>
       </c>
       <c r="D178" t="s">
@@ -5348,8 +6023,8 @@
       </c>
     </row>
     <row r="179" spans="1:4" ht="16" customHeight="1">
-      <c r="A179" s="36"/>
-      <c r="B179" s="5" t="s">
+      <c r="A179" s="35"/>
+      <c r="B179" s="14" t="s">
         <v>110</v>
       </c>
       <c r="D179" t="s">
@@ -5357,7 +6032,7 @@
       </c>
     </row>
     <row r="180" spans="1:4" ht="16" customHeight="1">
-      <c r="A180" s="38">
+      <c r="A180" s="23">
         <v>11</v>
       </c>
       <c r="B180" s="6" t="s">
@@ -5368,61 +6043,61 @@
       </c>
     </row>
     <row r="181" spans="1:4" ht="16" customHeight="1">
-      <c r="A181" s="38"/>
-      <c r="B181" s="3" t="s">
-        <v>189</v>
+      <c r="A181" s="23"/>
+      <c r="B181" s="12" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="16" customHeight="1">
-      <c r="A182" s="38"/>
+      <c r="A182" s="23"/>
       <c r="B182" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="16" customHeight="1">
-      <c r="A183" s="38"/>
-      <c r="B183" s="4" t="s">
+      <c r="A183" s="23"/>
+      <c r="B183" s="13" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="16" customHeight="1">
-      <c r="A184" s="38"/>
-      <c r="B184" s="5" t="s">
+      <c r="A184" s="23"/>
+      <c r="B184" s="14" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="16" customHeight="1">
-      <c r="A185" s="38"/>
-      <c r="B185" s="5" t="s">
+      <c r="A185" s="23"/>
+      <c r="B185" s="14" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="16" customHeight="1">
-      <c r="A186" s="38"/>
-      <c r="B186" s="4" t="s">
-        <v>194</v>
+      <c r="A186" s="23"/>
+      <c r="B186" s="13" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="187" spans="1:4" ht="16" customHeight="1">
-      <c r="A187" s="38"/>
+      <c r="A187" s="23"/>
       <c r="B187" s="4" t="s">
-        <v>195</v>
+        <v>365</v>
       </c>
     </row>
     <row r="188" spans="1:4" ht="16" customHeight="1">
-      <c r="A188" s="38"/>
-      <c r="B188" s="4" t="s">
-        <v>196</v>
+      <c r="A188" s="23"/>
+      <c r="B188" s="13" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="189" spans="1:4" ht="16" customHeight="1">
-      <c r="A189" s="38"/>
+      <c r="A189" s="23"/>
       <c r="B189" s="4" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="190" spans="1:4" ht="16" customHeight="1">
-      <c r="A190" s="26">
+      <c r="A190" s="25">
         <v>12</v>
       </c>
       <c r="B190" s="6" t="s">
@@ -5433,55 +6108,55 @@
       </c>
     </row>
     <row r="191" spans="1:4" ht="16" customHeight="1">
-      <c r="A191" s="26"/>
+      <c r="A191" s="25"/>
       <c r="B191" s="3" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="192" spans="1:4" ht="16" customHeight="1">
-      <c r="A192" s="26"/>
+      <c r="A192" s="25"/>
       <c r="B192" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="193" spans="1:4" ht="16" customHeight="1">
-      <c r="A193" s="26"/>
+      <c r="A193" s="25"/>
       <c r="B193" s="4" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="194" spans="1:4" ht="16" customHeight="1">
-      <c r="A194" s="26"/>
+      <c r="A194" s="25"/>
       <c r="B194" s="5" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="195" spans="1:4" ht="16" customHeight="1">
-      <c r="A195" s="26"/>
+      <c r="A195" s="25"/>
       <c r="B195" s="5" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="16" customHeight="1">
-      <c r="A196" s="26"/>
+      <c r="A196" s="25"/>
       <c r="B196" s="4" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="197" spans="1:4" ht="16" customHeight="1">
-      <c r="A197" s="26"/>
+      <c r="A197" s="25"/>
       <c r="B197" s="5" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="198" spans="1:4" ht="16" customHeight="1">
-      <c r="A198" s="26"/>
+      <c r="A198" s="25"/>
       <c r="B198" s="5" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="199" spans="1:4" ht="16" customHeight="1">
-      <c r="A199" s="26"/>
+      <c r="A199" s="25"/>
       <c r="B199" s="4" t="s">
         <v>198</v>
       </c>
@@ -5490,7 +6165,7 @@
       </c>
     </row>
     <row r="200" spans="1:4" ht="16" customHeight="1">
-      <c r="A200" s="26"/>
+      <c r="A200" s="25"/>
       <c r="B200" s="4" t="s">
         <v>199</v>
       </c>
@@ -5499,8 +6174,8 @@
       </c>
     </row>
     <row r="201" spans="1:4" ht="16" customHeight="1">
-      <c r="A201" s="26"/>
-      <c r="B201" s="6" t="s">
+      <c r="A201" s="25"/>
+      <c r="B201" s="19" t="s">
         <v>122</v>
       </c>
       <c r="C201" s="9">
@@ -5508,51 +6183,51 @@
       </c>
     </row>
     <row r="202" spans="1:4" ht="16" customHeight="1">
-      <c r="A202" s="37">
+      <c r="A202" s="22">
         <v>13</v>
       </c>
-      <c r="B202" s="3" t="s">
-        <v>191</v>
+      <c r="B202" s="12" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="203" spans="1:4" ht="16" customHeight="1">
-      <c r="A203" s="37"/>
-      <c r="B203" s="2" t="s">
+      <c r="A203" s="22"/>
+      <c r="B203" s="18" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="204" spans="1:4" ht="16" customHeight="1">
-      <c r="A204" s="37"/>
-      <c r="B204" s="4" t="s">
-        <v>200</v>
+      <c r="A204" s="22"/>
+      <c r="B204" s="13" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="16" customHeight="1">
-      <c r="A205" s="37"/>
-      <c r="B205" s="4" t="s">
-        <v>201</v>
+      <c r="A205" s="22"/>
+      <c r="B205" s="13" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="206" spans="1:4" ht="16" customHeight="1">
-      <c r="A206" s="37"/>
-      <c r="B206" s="4" t="s">
-        <v>202</v>
+      <c r="A206" s="22"/>
+      <c r="B206" s="13" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="207" spans="1:4" ht="16" customHeight="1">
-      <c r="A207" s="37"/>
-      <c r="B207" s="4" t="s">
-        <v>203</v>
+      <c r="A207" s="22"/>
+      <c r="B207" s="13" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="16" customHeight="1">
-      <c r="A208" s="37"/>
-      <c r="B208" s="4" t="s">
-        <v>204</v>
+      <c r="A208" s="22"/>
+      <c r="B208" s="13" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="209" spans="1:5" ht="16" customHeight="1">
-      <c r="A209" s="20">
+      <c r="A209" s="37">
         <v>14</v>
       </c>
       <c r="B209" s="6" t="s">
@@ -5563,61 +6238,61 @@
       </c>
     </row>
     <row r="210" spans="1:5" ht="16" customHeight="1">
-      <c r="A210" s="20"/>
-      <c r="B210" s="3" t="s">
-        <v>192</v>
+      <c r="A210" s="37"/>
+      <c r="B210" s="12" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="211" spans="1:5" ht="16" customHeight="1">
-      <c r="A211" s="20"/>
+      <c r="A211" s="37"/>
       <c r="B211" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="212" spans="1:5" ht="16" customHeight="1">
-      <c r="A212" s="20"/>
-      <c r="B212" s="4" t="s">
-        <v>205</v>
+      <c r="A212" s="37"/>
+      <c r="B212" s="13" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="213" spans="1:5" ht="16" customHeight="1">
-      <c r="A213" s="20"/>
-      <c r="B213" s="4" t="s">
-        <v>206</v>
+      <c r="A213" s="37"/>
+      <c r="B213" s="13" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="214" spans="1:5" ht="16" customHeight="1">
-      <c r="A214" s="20"/>
-      <c r="B214" s="4" t="s">
-        <v>207</v>
+      <c r="A214" s="37"/>
+      <c r="B214" s="13" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="215" spans="1:5" ht="16" customHeight="1">
-      <c r="A215" s="20"/>
-      <c r="B215" s="4" t="s">
-        <v>208</v>
+      <c r="A215" s="37"/>
+      <c r="B215" s="13" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="216" spans="1:5" ht="16" customHeight="1">
-      <c r="A216" s="20"/>
+      <c r="A216" s="37"/>
       <c r="B216" s="4" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="217" spans="1:5" ht="16" customHeight="1">
-      <c r="A217" s="20"/>
+      <c r="A217" s="37"/>
       <c r="B217" s="4" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="218" spans="1:5" ht="16" customHeight="1">
-      <c r="A218" s="20"/>
+      <c r="A218" s="37"/>
       <c r="B218" s="4" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="219" spans="1:5" ht="16" customHeight="1">
-      <c r="A219" s="20"/>
+      <c r="A219" s="37"/>
       <c r="B219" s="4" t="s">
         <v>212</v>
       </c>
@@ -5626,7 +6301,7 @@
       </c>
     </row>
     <row r="220" spans="1:5" ht="16" customHeight="1">
-      <c r="A220" s="20"/>
+      <c r="A220" s="37"/>
       <c r="B220" s="4" t="s">
         <v>213</v>
       </c>
@@ -5635,7 +6310,7 @@
       </c>
     </row>
     <row r="221" spans="1:5" ht="16" customHeight="1">
-      <c r="A221" s="21">
+      <c r="A221" s="38">
         <v>15</v>
       </c>
       <c r="B221" s="6" t="s">
@@ -5646,19 +6321,19 @@
       </c>
     </row>
     <row r="222" spans="1:5" ht="16" customHeight="1">
-      <c r="A222" s="21"/>
+      <c r="A222" s="38"/>
       <c r="B222" s="3" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="223" spans="1:5" ht="16" customHeight="1">
-      <c r="A223" s="21"/>
+      <c r="A223" s="38"/>
       <c r="B223" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="224" spans="1:5" ht="16" customHeight="1">
-      <c r="A224" s="21"/>
+      <c r="A224" s="38"/>
       <c r="B224" s="4" t="s">
         <v>214</v>
       </c>
@@ -5667,37 +6342,37 @@
       </c>
     </row>
     <row r="225" spans="1:4" ht="16" customHeight="1">
-      <c r="A225" s="21"/>
+      <c r="A225" s="38"/>
       <c r="B225" s="4" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="226" spans="1:4" ht="16" customHeight="1">
-      <c r="A226" s="21"/>
+      <c r="A226" s="38"/>
       <c r="B226" s="4" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="227" spans="1:4" ht="16" customHeight="1">
-      <c r="A227" s="21"/>
+      <c r="A227" s="38"/>
       <c r="B227" s="4" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="228" spans="1:4" ht="16" customHeight="1">
-      <c r="A228" s="21"/>
+      <c r="A228" s="38"/>
       <c r="B228" s="4" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="229" spans="1:4" ht="16" customHeight="1">
-      <c r="A229" s="21"/>
+      <c r="A229" s="38"/>
       <c r="B229" s="4" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="230" spans="1:4" ht="16" customHeight="1">
-      <c r="A230" s="22">
+      <c r="A230" s="39">
         <v>16</v>
       </c>
       <c r="B230" s="6" t="s">
@@ -5708,49 +6383,49 @@
       </c>
     </row>
     <row r="231" spans="1:4" ht="16" customHeight="1">
-      <c r="A231" s="22"/>
+      <c r="A231" s="39"/>
       <c r="B231" s="3" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="232" spans="1:4" ht="16" customHeight="1">
-      <c r="A232" s="22"/>
+      <c r="A232" s="39"/>
       <c r="B232" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="233" spans="1:4" ht="16" customHeight="1">
-      <c r="A233" s="22"/>
+      <c r="A233" s="39"/>
       <c r="B233" s="4" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="234" spans="1:4" ht="16" customHeight="1">
-      <c r="A234" s="22"/>
+      <c r="A234" s="39"/>
       <c r="B234" s="4" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="235" spans="1:4" ht="16" customHeight="1">
-      <c r="A235" s="22"/>
+      <c r="A235" s="39"/>
       <c r="B235" s="4" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="236" spans="1:4" ht="16" customHeight="1">
-      <c r="A236" s="22"/>
+      <c r="A236" s="39"/>
       <c r="B236" s="4" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="237" spans="1:4" ht="16" customHeight="1">
-      <c r="A237" s="22"/>
+      <c r="A237" s="39"/>
       <c r="B237" s="4" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="238" spans="1:4" ht="16" customHeight="1">
-      <c r="A238" s="22"/>
+      <c r="A238" s="39"/>
       <c r="B238" s="4" t="s">
         <v>226</v>
       </c>
@@ -5759,7 +6434,7 @@
       </c>
     </row>
     <row r="239" spans="1:4" ht="16" customHeight="1">
-      <c r="A239" s="23">
+      <c r="A239" s="40">
         <v>17</v>
       </c>
       <c r="B239" s="6" t="s">
@@ -5770,25 +6445,25 @@
       </c>
     </row>
     <row r="240" spans="1:4" ht="16" customHeight="1">
-      <c r="A240" s="23"/>
+      <c r="A240" s="40"/>
       <c r="B240" s="3" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="241" spans="1:5" ht="16" customHeight="1">
-      <c r="A241" s="23"/>
+      <c r="A241" s="40"/>
       <c r="B241" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="242" spans="1:5" ht="16" customHeight="1">
-      <c r="A242" s="23"/>
+      <c r="A242" s="40"/>
       <c r="B242" s="4" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="243" spans="1:5" ht="16" customHeight="1">
-      <c r="A243" s="23"/>
+      <c r="A243" s="40"/>
       <c r="B243" s="5" t="s">
         <v>128</v>
       </c>
@@ -5797,25 +6472,25 @@
       </c>
     </row>
     <row r="244" spans="1:5" ht="16" customHeight="1">
-      <c r="A244" s="23"/>
+      <c r="A244" s="40"/>
       <c r="B244" s="5" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="245" spans="1:5" ht="16" customHeight="1">
-      <c r="A245" s="23"/>
+      <c r="A245" s="40"/>
       <c r="B245" s="4" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="246" spans="1:5" ht="16" customHeight="1">
-      <c r="A246" s="23"/>
+      <c r="A246" s="40"/>
       <c r="B246" s="4" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="247" spans="1:5" ht="16" customHeight="1">
-      <c r="A247" s="23"/>
+      <c r="A247" s="40"/>
       <c r="B247" s="4" t="s">
         <v>230</v>
       </c>
@@ -5824,7 +6499,7 @@
       </c>
     </row>
     <row r="248" spans="1:5" ht="16" customHeight="1">
-      <c r="A248" s="23"/>
+      <c r="A248" s="40"/>
       <c r="B248" s="4" t="s">
         <v>231</v>
       </c>
@@ -5867,7 +6542,44 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="47">
+  <mergeCells count="53">
+    <mergeCell ref="E120:E122"/>
+    <mergeCell ref="A209:A220"/>
+    <mergeCell ref="A221:A229"/>
+    <mergeCell ref="A230:A238"/>
+    <mergeCell ref="A239:A248"/>
+    <mergeCell ref="E129:E131"/>
+    <mergeCell ref="E132:E135"/>
+    <mergeCell ref="E138:E145"/>
+    <mergeCell ref="E146:E149"/>
+    <mergeCell ref="E150:E155"/>
+    <mergeCell ref="E156:E167"/>
+    <mergeCell ref="E82:E84"/>
+    <mergeCell ref="E85:E87"/>
+    <mergeCell ref="E88:E90"/>
+    <mergeCell ref="E91:E93"/>
+    <mergeCell ref="E94:E96"/>
+    <mergeCell ref="E97:E99"/>
+    <mergeCell ref="E100:E103"/>
+    <mergeCell ref="E104:E106"/>
+    <mergeCell ref="E107:E109"/>
+    <mergeCell ref="E110:E113"/>
+    <mergeCell ref="E114:E116"/>
+    <mergeCell ref="E117:E119"/>
+    <mergeCell ref="D3:D12"/>
+    <mergeCell ref="A190:A201"/>
+    <mergeCell ref="A2:A34"/>
+    <mergeCell ref="A35:A48"/>
+    <mergeCell ref="A49:A60"/>
+    <mergeCell ref="A61:A69"/>
+    <mergeCell ref="A70:A82"/>
+    <mergeCell ref="A83:A95"/>
+    <mergeCell ref="A96:A131"/>
+    <mergeCell ref="A132:A151"/>
+    <mergeCell ref="A152:A167"/>
+    <mergeCell ref="A168:A179"/>
+    <mergeCell ref="E3:E12"/>
+    <mergeCell ref="E13:E21"/>
     <mergeCell ref="E28:E34"/>
     <mergeCell ref="E22:E27"/>
     <mergeCell ref="A202:A208"/>
@@ -5884,37 +6596,6 @@
     <mergeCell ref="E78:E80"/>
     <mergeCell ref="E123:E125"/>
     <mergeCell ref="E126:E128"/>
-    <mergeCell ref="E114:E116"/>
-    <mergeCell ref="E117:E119"/>
-    <mergeCell ref="D3:D12"/>
-    <mergeCell ref="A190:A201"/>
-    <mergeCell ref="A2:A34"/>
-    <mergeCell ref="A35:A48"/>
-    <mergeCell ref="A49:A60"/>
-    <mergeCell ref="A61:A69"/>
-    <mergeCell ref="A70:A82"/>
-    <mergeCell ref="A83:A95"/>
-    <mergeCell ref="A96:A131"/>
-    <mergeCell ref="A132:A151"/>
-    <mergeCell ref="A152:A167"/>
-    <mergeCell ref="A168:A179"/>
-    <mergeCell ref="E3:E12"/>
-    <mergeCell ref="E13:E21"/>
-    <mergeCell ref="E97:E99"/>
-    <mergeCell ref="E100:E103"/>
-    <mergeCell ref="E104:E106"/>
-    <mergeCell ref="E107:E109"/>
-    <mergeCell ref="E110:E113"/>
-    <mergeCell ref="E82:E84"/>
-    <mergeCell ref="E85:E87"/>
-    <mergeCell ref="E88:E90"/>
-    <mergeCell ref="E91:E93"/>
-    <mergeCell ref="E94:E96"/>
-    <mergeCell ref="E120:E122"/>
-    <mergeCell ref="A209:A220"/>
-    <mergeCell ref="A221:A229"/>
-    <mergeCell ref="A230:A238"/>
-    <mergeCell ref="A239:A248"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5941,7 +6622,7 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="16" customHeight="1">
-      <c r="A2" s="27">
+      <c r="A2" s="26">
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
@@ -5952,200 +6633,200 @@
       </c>
     </row>
     <row r="3" spans="1:4" ht="16" customHeight="1">
-      <c r="A3" s="27"/>
+      <c r="A3" s="26"/>
       <c r="B3" s="3" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="16" customHeight="1">
-      <c r="A4" s="27"/>
+      <c r="A4" s="26"/>
       <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="16" customHeight="1">
-      <c r="A5" s="27"/>
+      <c r="A5" s="26"/>
       <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="16" customHeight="1">
-      <c r="A6" s="27"/>
+      <c r="A6" s="26"/>
       <c r="B6" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="16" customHeight="1">
-      <c r="A7" s="27"/>
+      <c r="A7" s="26"/>
       <c r="B7" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="16" customHeight="1">
-      <c r="A8" s="27"/>
+      <c r="A8" s="26"/>
       <c r="B8" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="16" customHeight="1">
-      <c r="A9" s="27"/>
+      <c r="A9" s="26"/>
       <c r="B9" s="4" t="s">
         <v>154</v>
       </c>
       <c r="D9" s="10"/>
     </row>
     <row r="10" spans="1:4" ht="16" customHeight="1">
-      <c r="A10" s="27"/>
+      <c r="A10" s="26"/>
       <c r="B10" s="5" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="16" customHeight="1">
-      <c r="A11" s="27"/>
+      <c r="A11" s="26"/>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="16" customHeight="1">
-      <c r="A12" s="27"/>
+      <c r="A12" s="26"/>
       <c r="B12" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="16" customHeight="1">
-      <c r="A13" s="27"/>
+      <c r="A13" s="26"/>
       <c r="B13" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="16" customHeight="1">
-      <c r="A14" s="27"/>
+      <c r="A14" s="26"/>
       <c r="B14" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="16" customHeight="1">
-      <c r="A15" s="27"/>
+      <c r="A15" s="26"/>
       <c r="B15" s="5" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="16" customHeight="1">
-      <c r="A16" s="27"/>
+      <c r="A16" s="26"/>
       <c r="B16" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="16" customHeight="1">
-      <c r="A17" s="27"/>
+      <c r="A17" s="26"/>
       <c r="B17" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="16" customHeight="1">
-      <c r="A18" s="27"/>
+      <c r="A18" s="26"/>
       <c r="B18" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="16" customHeight="1">
-      <c r="A19" s="27"/>
+      <c r="A19" s="26"/>
       <c r="B19" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="16" customHeight="1">
-      <c r="A20" s="27"/>
+      <c r="A20" s="26"/>
       <c r="B20" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="16" customHeight="1">
-      <c r="A21" s="27"/>
+      <c r="A21" s="26"/>
       <c r="B21" s="5" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="16" customHeight="1">
-      <c r="A22" s="27"/>
+      <c r="A22" s="26"/>
       <c r="B22" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="16" customHeight="1">
-      <c r="A23" s="27"/>
+      <c r="A23" s="26"/>
       <c r="B23" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="16" customHeight="1">
-      <c r="A24" s="27"/>
+      <c r="A24" s="26"/>
       <c r="B24" s="5" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="16" customHeight="1">
-      <c r="A25" s="27"/>
+      <c r="A25" s="26"/>
       <c r="B25" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="16" customHeight="1">
-      <c r="A26" s="27"/>
+      <c r="A26" s="26"/>
       <c r="B26" s="4" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="16" customHeight="1">
-      <c r="A27" s="27"/>
+      <c r="A27" s="26"/>
       <c r="B27" s="4" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="16" customHeight="1">
-      <c r="A28" s="27"/>
+      <c r="A28" s="26"/>
       <c r="B28" s="4" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="16" customHeight="1">
-      <c r="A29" s="27"/>
+      <c r="A29" s="26"/>
       <c r="B29" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="16" customHeight="1">
-      <c r="A30" s="27"/>
+      <c r="A30" s="26"/>
       <c r="B30" s="5" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="16" customHeight="1">
-      <c r="A31" s="27"/>
+      <c r="A31" s="26"/>
       <c r="B31" s="4" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="16" customHeight="1">
-      <c r="A32" s="27"/>
+      <c r="A32" s="26"/>
       <c r="B32" s="5" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="16" customHeight="1">
-      <c r="A33" s="27"/>
+      <c r="A33" s="26"/>
       <c r="B33" s="5" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="16" customHeight="1">
-      <c r="A34" s="27"/>
+      <c r="A34" s="26"/>
       <c r="B34" s="5" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="16" customHeight="1">
-      <c r="A35" s="28">
+      <c r="A35" s="27">
         <v>2</v>
       </c>
       <c r="B35" s="6" t="s">
@@ -6156,85 +6837,85 @@
       </c>
     </row>
     <row r="36" spans="1:3" ht="29">
-      <c r="A36" s="28"/>
+      <c r="A36" s="27"/>
       <c r="B36" s="3" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="16" customHeight="1">
-      <c r="A37" s="28"/>
+      <c r="A37" s="27"/>
       <c r="B37" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="16" customHeight="1">
-      <c r="A38" s="28"/>
+      <c r="A38" s="27"/>
       <c r="B38" s="4" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="16" customHeight="1">
-      <c r="A39" s="28"/>
+      <c r="A39" s="27"/>
       <c r="B39" s="4" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="16" customHeight="1">
-      <c r="A40" s="28"/>
+      <c r="A40" s="27"/>
       <c r="B40" s="4" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="16" customHeight="1">
-      <c r="A41" s="28"/>
+      <c r="A41" s="27"/>
       <c r="B41" s="5" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="16" customHeight="1">
-      <c r="A42" s="28"/>
+      <c r="A42" s="27"/>
       <c r="B42" s="5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="16" customHeight="1">
-      <c r="A43" s="28"/>
+      <c r="A43" s="27"/>
       <c r="B43" s="4" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="16" customHeight="1">
-      <c r="A44" s="28"/>
+      <c r="A44" s="27"/>
       <c r="B44" s="4" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="16" customHeight="1">
-      <c r="A45" s="28"/>
+      <c r="A45" s="27"/>
       <c r="B45" s="4" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="16" customHeight="1">
-      <c r="A46" s="28"/>
+      <c r="A46" s="27"/>
       <c r="B46" s="5" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="16" customHeight="1">
-      <c r="A47" s="28"/>
+      <c r="A47" s="27"/>
       <c r="B47" s="5" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="16" customHeight="1">
-      <c r="A48" s="28"/>
+      <c r="A48" s="27"/>
       <c r="B48" s="4" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="16" customHeight="1">
-      <c r="A49" s="29">
+      <c r="A49" s="28">
         <v>3</v>
       </c>
       <c r="B49" s="6" t="s">
@@ -6245,73 +6926,73 @@
       </c>
     </row>
     <row r="50" spans="1:3" ht="16" customHeight="1">
-      <c r="A50" s="29"/>
+      <c r="A50" s="28"/>
       <c r="B50" s="3" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="16" customHeight="1">
-      <c r="A51" s="29"/>
+      <c r="A51" s="28"/>
       <c r="B51" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="16" customHeight="1">
-      <c r="A52" s="29"/>
+      <c r="A52" s="28"/>
       <c r="B52" s="4" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="16" customHeight="1">
-      <c r="A53" s="29"/>
+      <c r="A53" s="28"/>
       <c r="B53" s="4" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="16" customHeight="1">
-      <c r="A54" s="29"/>
+      <c r="A54" s="28"/>
       <c r="B54" s="4" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="16" customHeight="1">
-      <c r="A55" s="29"/>
+      <c r="A55" s="28"/>
       <c r="B55" s="4" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="16" customHeight="1">
-      <c r="A56" s="29"/>
+      <c r="A56" s="28"/>
       <c r="B56" s="4" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="16" customHeight="1">
-      <c r="A57" s="29"/>
+      <c r="A57" s="28"/>
       <c r="B57" s="4" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="16" customHeight="1">
-      <c r="A58" s="29"/>
+      <c r="A58" s="28"/>
       <c r="B58" s="5" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="16" customHeight="1">
-      <c r="A59" s="29"/>
+      <c r="A59" s="28"/>
       <c r="B59" s="5" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="16" customHeight="1">
-      <c r="A60" s="29"/>
+      <c r="A60" s="28"/>
       <c r="B60" s="4" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="16" customHeight="1">
-      <c r="A61" s="30">
+      <c r="A61" s="29">
         <v>4</v>
       </c>
       <c r="B61" s="6" t="s">
@@ -6322,55 +7003,55 @@
       </c>
     </row>
     <row r="62" spans="1:3" ht="16" customHeight="1">
-      <c r="A62" s="30"/>
+      <c r="A62" s="29"/>
       <c r="B62" s="3" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="16" customHeight="1">
-      <c r="A63" s="30"/>
+      <c r="A63" s="29"/>
       <c r="B63" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="16" customHeight="1">
-      <c r="A64" s="30"/>
+      <c r="A64" s="29"/>
       <c r="B64" s="4" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="16" customHeight="1">
-      <c r="A65" s="30"/>
+      <c r="A65" s="29"/>
       <c r="B65" s="4" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="16" customHeight="1">
-      <c r="A66" s="30"/>
+      <c r="A66" s="29"/>
       <c r="B66" s="4" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="16" customHeight="1">
-      <c r="A67" s="30"/>
+      <c r="A67" s="29"/>
       <c r="B67" s="4" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="16" customHeight="1">
-      <c r="A68" s="30"/>
+      <c r="A68" s="29"/>
       <c r="B68" s="4" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="16" customHeight="1">
-      <c r="A69" s="30"/>
+      <c r="A69" s="29"/>
       <c r="B69" s="4" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="16" customHeight="1">
-      <c r="A70" s="31">
+      <c r="A70" s="30">
         <v>5</v>
       </c>
       <c r="B70" s="6" t="s">
@@ -6381,91 +7062,91 @@
       </c>
     </row>
     <row r="71" spans="1:3" ht="16" customHeight="1">
-      <c r="A71" s="31"/>
+      <c r="A71" s="30"/>
       <c r="B71" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="16" customHeight="1">
-      <c r="A72" s="31"/>
+      <c r="A72" s="30"/>
       <c r="B72" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="16" customHeight="1">
-      <c r="A73" s="31"/>
+      <c r="A73" s="30"/>
       <c r="B73" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="16" customHeight="1">
-      <c r="A74" s="31"/>
+      <c r="A74" s="30"/>
       <c r="B74" s="4" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="16" customHeight="1">
-      <c r="A75" s="31"/>
+      <c r="A75" s="30"/>
       <c r="B75" s="4" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="16" customHeight="1">
-      <c r="A76" s="31"/>
+      <c r="A76" s="30"/>
       <c r="B76" s="4" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="16" customHeight="1">
-      <c r="A77" s="31"/>
+      <c r="A77" s="30"/>
       <c r="B77" s="4" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="16" customHeight="1">
-      <c r="A78" s="31"/>
+      <c r="A78" s="30"/>
       <c r="B78" s="4" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="16" customHeight="1">
-      <c r="A79" s="31"/>
+      <c r="A79" s="30"/>
       <c r="B79" s="4" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="16" customHeight="1">
-      <c r="A80" s="31"/>
+      <c r="A80" s="30"/>
       <c r="B80" s="4" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="16" customHeight="1">
-      <c r="A81" s="31"/>
+      <c r="A81" s="30"/>
       <c r="B81" s="4" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="16" customHeight="1">
-      <c r="A82" s="31"/>
+      <c r="A82" s="30"/>
       <c r="B82" s="4" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="16" customHeight="1">
-      <c r="A83" s="31"/>
+      <c r="A83" s="30"/>
       <c r="B83" s="4" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="16" customHeight="1">
-      <c r="A84" s="31"/>
+      <c r="A84" s="30"/>
       <c r="B84" s="4" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="16" customHeight="1">
-      <c r="A85" s="32">
+      <c r="A85" s="31">
         <v>6</v>
       </c>
       <c r="B85" s="6" t="s">
@@ -6476,79 +7157,79 @@
       </c>
     </row>
     <row r="86" spans="1:3" ht="16" customHeight="1">
-      <c r="A86" s="32"/>
+      <c r="A86" s="31"/>
       <c r="B86" s="3" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="16" customHeight="1">
-      <c r="A87" s="32"/>
+      <c r="A87" s="31"/>
       <c r="B87" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="16" customHeight="1">
-      <c r="A88" s="32"/>
+      <c r="A88" s="31"/>
       <c r="B88" s="4" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="16" customHeight="1">
-      <c r="A89" s="32"/>
+      <c r="A89" s="31"/>
       <c r="B89" s="4" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="16" customHeight="1">
-      <c r="A90" s="32"/>
+      <c r="A90" s="31"/>
       <c r="B90" s="4" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="16" customHeight="1">
-      <c r="A91" s="32"/>
+      <c r="A91" s="31"/>
       <c r="B91" s="4" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="16" customHeight="1">
-      <c r="A92" s="32"/>
+      <c r="A92" s="31"/>
       <c r="B92" s="4" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="16" customHeight="1">
-      <c r="A93" s="32"/>
+      <c r="A93" s="31"/>
       <c r="B93" s="4" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="16" customHeight="1">
-      <c r="A94" s="32"/>
+      <c r="A94" s="31"/>
       <c r="B94" s="4" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="16" customHeight="1">
-      <c r="A95" s="32"/>
+      <c r="A95" s="31"/>
       <c r="B95" s="4" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="16" customHeight="1">
-      <c r="A96" s="32"/>
+      <c r="A96" s="31"/>
       <c r="B96" s="4" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="16" customHeight="1">
-      <c r="A97" s="32"/>
+      <c r="A97" s="31"/>
       <c r="B97" s="4" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="16" customHeight="1">
-      <c r="A98" s="33">
+      <c r="A98" s="32">
         <v>7</v>
       </c>
       <c r="B98" s="6" t="s">
@@ -6559,217 +7240,217 @@
       </c>
     </row>
     <row r="99" spans="1:3" ht="33" customHeight="1">
-      <c r="A99" s="33"/>
+      <c r="A99" s="32"/>
       <c r="B99" s="3" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="16" customHeight="1">
-      <c r="A100" s="33"/>
+      <c r="A100" s="32"/>
       <c r="B100" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="16" customHeight="1">
-      <c r="A101" s="33"/>
+      <c r="A101" s="32"/>
       <c r="B101" s="4" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="16" customHeight="1">
-      <c r="A102" s="33"/>
+      <c r="A102" s="32"/>
       <c r="B102" s="5" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="16" customHeight="1">
-      <c r="A103" s="33"/>
+      <c r="A103" s="32"/>
       <c r="B103" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="16" customHeight="1">
-      <c r="A104" s="33"/>
+      <c r="A104" s="32"/>
       <c r="B104" s="5" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="16" customHeight="1">
-      <c r="A105" s="33"/>
+      <c r="A105" s="32"/>
       <c r="B105" s="4" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="16" customHeight="1">
-      <c r="A106" s="33"/>
+      <c r="A106" s="32"/>
       <c r="B106" s="5" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="16" customHeight="1">
-      <c r="A107" s="33"/>
+      <c r="A107" s="32"/>
       <c r="B107" s="5" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="16" customHeight="1">
-      <c r="A108" s="33"/>
+      <c r="A108" s="32"/>
       <c r="B108" s="4" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="109" spans="1:3" ht="16" customHeight="1">
-      <c r="A109" s="33"/>
+      <c r="A109" s="32"/>
       <c r="B109" s="5" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="16" customHeight="1">
-      <c r="A110" s="33"/>
+      <c r="A110" s="32"/>
       <c r="B110" s="5" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="16" customHeight="1">
-      <c r="A111" s="33"/>
+      <c r="A111" s="32"/>
       <c r="B111" s="4" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="16" customHeight="1">
-      <c r="A112" s="33"/>
+      <c r="A112" s="32"/>
       <c r="B112" s="5" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="113" spans="1:2" ht="16" customHeight="1">
-      <c r="A113" s="33"/>
+      <c r="A113" s="32"/>
       <c r="B113" s="5" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="114" spans="1:2" ht="16" customHeight="1">
-      <c r="A114" s="33"/>
+      <c r="A114" s="32"/>
       <c r="B114" s="4" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="115" spans="1:2" ht="16" customHeight="1">
-      <c r="A115" s="33"/>
+      <c r="A115" s="32"/>
       <c r="B115" s="4" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="116" spans="1:2" ht="16" customHeight="1">
-      <c r="A116" s="33"/>
+      <c r="A116" s="32"/>
       <c r="B116" s="5" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="117" spans="1:2" ht="16" customHeight="1">
-      <c r="A117" s="33"/>
+      <c r="A117" s="32"/>
       <c r="B117" s="5" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="118" spans="1:2" ht="16" customHeight="1">
-      <c r="A118" s="33"/>
+      <c r="A118" s="32"/>
       <c r="B118" s="4" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="119" spans="1:2" ht="16" customHeight="1">
-      <c r="A119" s="33"/>
+      <c r="A119" s="32"/>
       <c r="B119" s="5" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="120" spans="1:2" ht="16" customHeight="1">
-      <c r="A120" s="33"/>
+      <c r="A120" s="32"/>
       <c r="B120" s="5" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="121" spans="1:2" ht="16" customHeight="1">
-      <c r="A121" s="33"/>
+      <c r="A121" s="32"/>
       <c r="B121" s="4" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="122" spans="1:2" ht="16" customHeight="1">
-      <c r="A122" s="33"/>
+      <c r="A122" s="32"/>
       <c r="B122" s="5" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="123" spans="1:2" ht="16" customHeight="1">
-      <c r="A123" s="33"/>
+      <c r="A123" s="32"/>
       <c r="B123" s="5" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="124" spans="1:2" ht="16" customHeight="1">
-      <c r="A124" s="33"/>
+      <c r="A124" s="32"/>
       <c r="B124" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="125" spans="1:2" ht="16" customHeight="1">
-      <c r="A125" s="33"/>
+      <c r="A125" s="32"/>
       <c r="B125" s="5" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="126" spans="1:2" ht="16" customHeight="1">
-      <c r="A126" s="33"/>
+      <c r="A126" s="32"/>
       <c r="B126" s="5" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="127" spans="1:2" ht="16" customHeight="1">
-      <c r="A127" s="33"/>
+      <c r="A127" s="32"/>
       <c r="B127" s="4" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="128" spans="1:2" ht="16" customHeight="1">
-      <c r="A128" s="33"/>
+      <c r="A128" s="32"/>
       <c r="B128" s="5" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="16" customHeight="1">
-      <c r="A129" s="33"/>
+      <c r="A129" s="32"/>
       <c r="B129" s="5" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="16" customHeight="1">
-      <c r="A130" s="33"/>
+      <c r="A130" s="32"/>
       <c r="B130" s="4" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="131" spans="1:3" ht="16" customHeight="1">
-      <c r="A131" s="33"/>
+      <c r="A131" s="32"/>
       <c r="B131" s="5" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="132" spans="1:3" ht="16" customHeight="1">
-      <c r="A132" s="33"/>
+      <c r="A132" s="32"/>
       <c r="B132" s="5" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="133" spans="1:3" ht="16" customHeight="1">
-      <c r="A133" s="33"/>
+      <c r="A133" s="32"/>
       <c r="B133" s="5" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="134" spans="1:3" ht="16" customHeight="1">
-      <c r="A134" s="34">
+      <c r="A134" s="33">
         <v>8</v>
       </c>
       <c r="B134" s="6" t="s">
@@ -6780,121 +7461,121 @@
       </c>
     </row>
     <row r="135" spans="1:3" ht="16" customHeight="1">
-      <c r="A135" s="34"/>
+      <c r="A135" s="33"/>
       <c r="B135" s="3" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="16" customHeight="1">
-      <c r="A136" s="34"/>
+      <c r="A136" s="33"/>
       <c r="B136" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="137" spans="1:3" ht="16" customHeight="1">
-      <c r="A137" s="34"/>
+      <c r="A137" s="33"/>
       <c r="B137" s="4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="138" spans="1:3" ht="16" customHeight="1">
-      <c r="A138" s="34"/>
+      <c r="A138" s="33"/>
       <c r="B138" s="5" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="139" spans="1:3" ht="16" customHeight="1">
-      <c r="A139" s="34"/>
+      <c r="A139" s="33"/>
       <c r="B139" s="5" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="140" spans="1:3" ht="16" customHeight="1">
-      <c r="A140" s="34"/>
+      <c r="A140" s="33"/>
       <c r="B140" s="4" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="141" spans="1:3" ht="16" customHeight="1">
-      <c r="A141" s="34"/>
+      <c r="A141" s="33"/>
       <c r="B141" s="5" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="142" spans="1:3" ht="16" customHeight="1">
-      <c r="A142" s="34"/>
+      <c r="A142" s="33"/>
       <c r="B142" s="5" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="143" spans="1:3" ht="16" customHeight="1">
-      <c r="A143" s="34"/>
+      <c r="A143" s="33"/>
       <c r="B143" s="4" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="144" spans="1:3" ht="16" customHeight="1">
-      <c r="A144" s="34"/>
+      <c r="A144" s="33"/>
       <c r="B144" s="5" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="145" spans="1:3" ht="16" customHeight="1">
-      <c r="A145" s="34"/>
+      <c r="A145" s="33"/>
       <c r="B145" s="5" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="146" spans="1:3" ht="16" customHeight="1">
-      <c r="A146" s="34"/>
+      <c r="A146" s="33"/>
       <c r="B146" s="4" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="16" customHeight="1">
-      <c r="A147" s="34"/>
+      <c r="A147" s="33"/>
       <c r="B147" s="5" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="148" spans="1:3" ht="16" customHeight="1">
-      <c r="A148" s="34"/>
+      <c r="A148" s="33"/>
       <c r="B148" s="5" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="149" spans="1:3" ht="16" customHeight="1">
-      <c r="A149" s="34"/>
+      <c r="A149" s="33"/>
       <c r="B149" s="4" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="150" spans="1:3" ht="16" customHeight="1">
-      <c r="A150" s="34"/>
+      <c r="A150" s="33"/>
       <c r="B150" s="5" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="151" spans="1:3" ht="16" customHeight="1">
-      <c r="A151" s="34"/>
+      <c r="A151" s="33"/>
       <c r="B151" s="4" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="152" spans="1:3" ht="16" customHeight="1">
-      <c r="A152" s="34"/>
+      <c r="A152" s="33"/>
       <c r="B152" s="5" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="153" spans="1:3" ht="16" customHeight="1">
-      <c r="A153" s="34"/>
+      <c r="A153" s="33"/>
       <c r="B153" s="5" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="154" spans="1:3" ht="16" customHeight="1">
-      <c r="A154" s="35">
+      <c r="A154" s="34">
         <v>9</v>
       </c>
       <c r="B154" s="6" t="s">
@@ -6905,97 +7586,97 @@
       </c>
     </row>
     <row r="155" spans="1:3" ht="16" customHeight="1">
-      <c r="A155" s="35"/>
+      <c r="A155" s="34"/>
       <c r="B155" s="3" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="156" spans="1:3" ht="16" customHeight="1">
-      <c r="A156" s="35"/>
+      <c r="A156" s="34"/>
       <c r="B156" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="157" spans="1:3" ht="16" customHeight="1">
-      <c r="A157" s="35"/>
+      <c r="A157" s="34"/>
       <c r="B157" s="4" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="158" spans="1:3" ht="16" customHeight="1">
-      <c r="A158" s="35"/>
+      <c r="A158" s="34"/>
       <c r="B158" s="5" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="159" spans="1:3" ht="16" customHeight="1">
-      <c r="A159" s="35"/>
+      <c r="A159" s="34"/>
       <c r="B159" s="5" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="160" spans="1:3" ht="16" customHeight="1">
-      <c r="A160" s="35"/>
+      <c r="A160" s="34"/>
       <c r="B160" s="4" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="161" spans="1:3" ht="16" customHeight="1">
-      <c r="A161" s="35"/>
+      <c r="A161" s="34"/>
       <c r="B161" s="5" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="162" spans="1:3" ht="16" customHeight="1">
-      <c r="A162" s="35"/>
+      <c r="A162" s="34"/>
       <c r="B162" s="5" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="163" spans="1:3" ht="16" customHeight="1">
-      <c r="A163" s="35"/>
+      <c r="A163" s="34"/>
       <c r="B163" s="4" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="164" spans="1:3" ht="16" customHeight="1">
-      <c r="A164" s="35"/>
+      <c r="A164" s="34"/>
       <c r="B164" s="5" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="165" spans="1:3" ht="16" customHeight="1">
-      <c r="A165" s="35"/>
+      <c r="A165" s="34"/>
       <c r="B165" s="5" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="166" spans="1:3" ht="16" customHeight="1">
-      <c r="A166" s="35"/>
+      <c r="A166" s="34"/>
       <c r="B166" s="4" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="167" spans="1:3" ht="16" customHeight="1">
-      <c r="A167" s="35"/>
+      <c r="A167" s="34"/>
       <c r="B167" s="4" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="168" spans="1:3" ht="16" customHeight="1">
-      <c r="A168" s="35"/>
+      <c r="A168" s="34"/>
       <c r="B168" s="4" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="169" spans="1:3" ht="16" customHeight="1">
-      <c r="A169" s="35"/>
+      <c r="A169" s="34"/>
       <c r="B169" s="4" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="170" spans="1:3" ht="16" customHeight="1">
-      <c r="A170" s="36">
+      <c r="A170" s="35">
         <v>10</v>
       </c>
       <c r="B170" s="6" t="s">
@@ -7006,73 +7687,73 @@
       </c>
     </row>
     <row r="171" spans="1:3" ht="16" customHeight="1">
-      <c r="A171" s="36"/>
+      <c r="A171" s="35"/>
       <c r="B171" s="3" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="172" spans="1:3" ht="16" customHeight="1">
-      <c r="A172" s="36"/>
+      <c r="A172" s="35"/>
       <c r="B172" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="173" spans="1:3" ht="16" customHeight="1">
-      <c r="A173" s="36"/>
+      <c r="A173" s="35"/>
       <c r="B173" s="4" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="174" spans="1:3" ht="16" customHeight="1">
-      <c r="A174" s="36"/>
+      <c r="A174" s="35"/>
       <c r="B174" s="5" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="175" spans="1:3" ht="16" customHeight="1">
-      <c r="A175" s="36"/>
+      <c r="A175" s="35"/>
       <c r="B175" s="5" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="176" spans="1:3" ht="16" customHeight="1">
-      <c r="A176" s="36"/>
+      <c r="A176" s="35"/>
       <c r="B176" s="4" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="177" spans="1:3" ht="16" customHeight="1">
-      <c r="A177" s="36"/>
+      <c r="A177" s="35"/>
       <c r="B177" s="5" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="178" spans="1:3" ht="16" customHeight="1">
-      <c r="A178" s="36"/>
+      <c r="A178" s="35"/>
       <c r="B178" s="5" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="179" spans="1:3" ht="16" customHeight="1">
-      <c r="A179" s="36"/>
+      <c r="A179" s="35"/>
       <c r="B179" s="4" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="180" spans="1:3" ht="16" customHeight="1">
-      <c r="A180" s="36"/>
+      <c r="A180" s="35"/>
       <c r="B180" s="5" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="181" spans="1:3" ht="16" customHeight="1">
-      <c r="A181" s="36"/>
+      <c r="A181" s="35"/>
       <c r="B181" s="5" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="182" spans="1:3" ht="16" customHeight="1">
-      <c r="A182" s="38">
+      <c r="A182" s="23">
         <v>11</v>
       </c>
       <c r="B182" s="6" t="s">
@@ -7083,61 +7764,61 @@
       </c>
     </row>
     <row r="183" spans="1:3" ht="16" customHeight="1">
-      <c r="A183" s="38"/>
+      <c r="A183" s="23"/>
       <c r="B183" s="3" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="184" spans="1:3" ht="16" customHeight="1">
-      <c r="A184" s="38"/>
+      <c r="A184" s="23"/>
       <c r="B184" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="16" customHeight="1">
-      <c r="A185" s="38"/>
+      <c r="A185" s="23"/>
       <c r="B185" s="4" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="186" spans="1:3" ht="16" customHeight="1">
-      <c r="A186" s="38"/>
+      <c r="A186" s="23"/>
       <c r="B186" s="5" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="187" spans="1:3" ht="16" customHeight="1">
-      <c r="A187" s="38"/>
+      <c r="A187" s="23"/>
       <c r="B187" s="5" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="188" spans="1:3" ht="16" customHeight="1">
-      <c r="A188" s="38"/>
+      <c r="A188" s="23"/>
       <c r="B188" s="4" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="189" spans="1:3" ht="16" customHeight="1">
-      <c r="A189" s="38"/>
+      <c r="A189" s="23"/>
       <c r="B189" s="4" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="190" spans="1:3" ht="16" customHeight="1">
-      <c r="A190" s="38"/>
+      <c r="A190" s="23"/>
       <c r="B190" s="4" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="16" customHeight="1">
-      <c r="A191" s="38"/>
+      <c r="A191" s="23"/>
       <c r="B191" s="4" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="192" spans="1:3" ht="16" customHeight="1">
-      <c r="A192" s="26">
+      <c r="A192" s="25">
         <v>12</v>
       </c>
       <c r="B192" s="6" t="s">
@@ -7148,67 +7829,67 @@
       </c>
     </row>
     <row r="193" spans="1:3" ht="16" customHeight="1">
-      <c r="A193" s="26"/>
+      <c r="A193" s="25"/>
       <c r="B193" s="3" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="194" spans="1:3" ht="16" customHeight="1">
-      <c r="A194" s="26"/>
+      <c r="A194" s="25"/>
       <c r="B194" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="195" spans="1:3" ht="16" customHeight="1">
-      <c r="A195" s="26"/>
+      <c r="A195" s="25"/>
       <c r="B195" s="4" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="16" customHeight="1">
-      <c r="A196" s="26"/>
+      <c r="A196" s="25"/>
       <c r="B196" s="5" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="197" spans="1:3" ht="16" customHeight="1">
-      <c r="A197" s="26"/>
+      <c r="A197" s="25"/>
       <c r="B197" s="5" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="198" spans="1:3" ht="16" customHeight="1">
-      <c r="A198" s="26"/>
+      <c r="A198" s="25"/>
       <c r="B198" s="4" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="199" spans="1:3" ht="16" customHeight="1">
-      <c r="A199" s="26"/>
+      <c r="A199" s="25"/>
       <c r="B199" s="5" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="200" spans="1:3" ht="16" customHeight="1">
-      <c r="A200" s="26"/>
+      <c r="A200" s="25"/>
       <c r="B200" s="5" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="201" spans="1:3" ht="16" customHeight="1">
-      <c r="A201" s="26"/>
+      <c r="A201" s="25"/>
       <c r="B201" s="4" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="202" spans="1:3" ht="16" customHeight="1">
-      <c r="A202" s="26"/>
+      <c r="A202" s="25"/>
       <c r="B202" s="4" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="203" spans="1:3" ht="16" customHeight="1">
-      <c r="A203" s="26"/>
+      <c r="A203" s="25"/>
       <c r="B203" s="6" t="s">
         <v>122</v>
       </c>
@@ -7217,7 +7898,7 @@
       </c>
     </row>
     <row r="204" spans="1:3" ht="16" customHeight="1">
-      <c r="A204" s="37">
+      <c r="A204" s="22">
         <v>13</v>
       </c>
       <c r="B204" s="3" t="s">
@@ -7225,43 +7906,43 @@
       </c>
     </row>
     <row r="205" spans="1:3" ht="16" customHeight="1">
-      <c r="A205" s="37"/>
+      <c r="A205" s="22"/>
       <c r="B205" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="206" spans="1:3" ht="16" customHeight="1">
-      <c r="A206" s="37"/>
+      <c r="A206" s="22"/>
       <c r="B206" s="4" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="207" spans="1:3" ht="16" customHeight="1">
-      <c r="A207" s="37"/>
+      <c r="A207" s="22"/>
       <c r="B207" s="4" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="208" spans="1:3" ht="16" customHeight="1">
-      <c r="A208" s="37"/>
+      <c r="A208" s="22"/>
       <c r="B208" s="4" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="209" spans="1:3" ht="16" customHeight="1">
-      <c r="A209" s="37"/>
+      <c r="A209" s="22"/>
       <c r="B209" s="4" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="210" spans="1:3" ht="16" customHeight="1">
-      <c r="A210" s="37"/>
+      <c r="A210" s="22"/>
       <c r="B210" s="4" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="211" spans="1:3" ht="16" customHeight="1">
-      <c r="A211" s="20">
+      <c r="A211" s="37">
         <v>14</v>
       </c>
       <c r="B211" s="6" t="s">
@@ -7272,73 +7953,73 @@
       </c>
     </row>
     <row r="212" spans="1:3" ht="16" customHeight="1">
-      <c r="A212" s="20"/>
+      <c r="A212" s="37"/>
       <c r="B212" s="3" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="213" spans="1:3" ht="16" customHeight="1">
-      <c r="A213" s="20"/>
+      <c r="A213" s="37"/>
       <c r="B213" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="214" spans="1:3" ht="16" customHeight="1">
-      <c r="A214" s="20"/>
+      <c r="A214" s="37"/>
       <c r="B214" s="4" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="215" spans="1:3" ht="16" customHeight="1">
-      <c r="A215" s="20"/>
+      <c r="A215" s="37"/>
       <c r="B215" s="4" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="216" spans="1:3" ht="16" customHeight="1">
-      <c r="A216" s="20"/>
+      <c r="A216" s="37"/>
       <c r="B216" s="4" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="217" spans="1:3" ht="16" customHeight="1">
-      <c r="A217" s="20"/>
+      <c r="A217" s="37"/>
       <c r="B217" s="4" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="218" spans="1:3" ht="16" customHeight="1">
-      <c r="A218" s="20"/>
+      <c r="A218" s="37"/>
       <c r="B218" s="4" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="219" spans="1:3" ht="16" customHeight="1">
-      <c r="A219" s="20"/>
+      <c r="A219" s="37"/>
       <c r="B219" s="4" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="220" spans="1:3" ht="16" customHeight="1">
-      <c r="A220" s="20"/>
+      <c r="A220" s="37"/>
       <c r="B220" s="4" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="221" spans="1:3" ht="16" customHeight="1">
-      <c r="A221" s="20"/>
+      <c r="A221" s="37"/>
       <c r="B221" s="4" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="222" spans="1:3" ht="16" customHeight="1">
-      <c r="A222" s="20"/>
+      <c r="A222" s="37"/>
       <c r="B222" s="4" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="223" spans="1:3" ht="16" customHeight="1">
-      <c r="A223" s="21">
+      <c r="A223" s="38">
         <v>15</v>
       </c>
       <c r="B223" s="6" t="s">
@@ -7349,55 +8030,55 @@
       </c>
     </row>
     <row r="224" spans="1:3" ht="16" customHeight="1">
-      <c r="A224" s="21"/>
+      <c r="A224" s="38"/>
       <c r="B224" s="3" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="225" spans="1:3" ht="16" customHeight="1">
-      <c r="A225" s="21"/>
+      <c r="A225" s="38"/>
       <c r="B225" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="226" spans="1:3" ht="16" customHeight="1">
-      <c r="A226" s="21"/>
+      <c r="A226" s="38"/>
       <c r="B226" s="4" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="227" spans="1:3" ht="16" customHeight="1">
-      <c r="A227" s="21"/>
+      <c r="A227" s="38"/>
       <c r="B227" s="4" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="228" spans="1:3" ht="16" customHeight="1">
-      <c r="A228" s="21"/>
+      <c r="A228" s="38"/>
       <c r="B228" s="4" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="229" spans="1:3" ht="16" customHeight="1">
-      <c r="A229" s="21"/>
+      <c r="A229" s="38"/>
       <c r="B229" s="4" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="230" spans="1:3" ht="16" customHeight="1">
-      <c r="A230" s="21"/>
+      <c r="A230" s="38"/>
       <c r="B230" s="4" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="231" spans="1:3" ht="16" customHeight="1">
-      <c r="A231" s="21"/>
+      <c r="A231" s="38"/>
       <c r="B231" s="4" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="232" spans="1:3" ht="16" customHeight="1">
-      <c r="A232" s="22">
+      <c r="A232" s="39">
         <v>16</v>
       </c>
       <c r="B232" s="6" t="s">
@@ -7408,55 +8089,55 @@
       </c>
     </row>
     <row r="233" spans="1:3" ht="16" customHeight="1">
-      <c r="A233" s="22"/>
+      <c r="A233" s="39"/>
       <c r="B233" s="3" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="234" spans="1:3" ht="16" customHeight="1">
-      <c r="A234" s="22"/>
+      <c r="A234" s="39"/>
       <c r="B234" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="235" spans="1:3" ht="16" customHeight="1">
-      <c r="A235" s="22"/>
+      <c r="A235" s="39"/>
       <c r="B235" s="4" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="236" spans="1:3" ht="16" customHeight="1">
-      <c r="A236" s="22"/>
+      <c r="A236" s="39"/>
       <c r="B236" s="4" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="237" spans="1:3" ht="16" customHeight="1">
-      <c r="A237" s="22"/>
+      <c r="A237" s="39"/>
       <c r="B237" s="4" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="238" spans="1:3" ht="16" customHeight="1">
-      <c r="A238" s="22"/>
+      <c r="A238" s="39"/>
       <c r="B238" s="4" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="239" spans="1:3" ht="16" customHeight="1">
-      <c r="A239" s="22"/>
+      <c r="A239" s="39"/>
       <c r="B239" s="4" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="240" spans="1:3" ht="16" customHeight="1">
-      <c r="A240" s="22"/>
+      <c r="A240" s="39"/>
       <c r="B240" s="4" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="241" spans="1:4" ht="16" customHeight="1">
-      <c r="A241" s="23">
+      <c r="A241" s="40">
         <v>17</v>
       </c>
       <c r="B241" s="6" t="s">
@@ -7467,43 +8148,43 @@
       </c>
     </row>
     <row r="242" spans="1:4" ht="16" customHeight="1">
-      <c r="A242" s="23"/>
+      <c r="A242" s="40"/>
       <c r="B242" s="3" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="243" spans="1:4" ht="16" customHeight="1">
-      <c r="A243" s="23"/>
+      <c r="A243" s="40"/>
       <c r="B243" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="244" spans="1:4" ht="16" customHeight="1">
-      <c r="A244" s="23"/>
+      <c r="A244" s="40"/>
       <c r="B244" s="4" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="245" spans="1:4" ht="16" customHeight="1">
-      <c r="A245" s="23"/>
+      <c r="A245" s="40"/>
       <c r="B245" s="5" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="246" spans="1:4" ht="16" customHeight="1">
-      <c r="A246" s="23"/>
+      <c r="A246" s="40"/>
       <c r="B246" s="5" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="247" spans="1:4" ht="16" customHeight="1">
-      <c r="A247" s="23"/>
+      <c r="A247" s="40"/>
       <c r="B247" s="4" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="248" spans="1:4" ht="16" customHeight="1">
-      <c r="A248" s="23"/>
+      <c r="A248" s="40"/>
       <c r="B248" s="4" t="s">
         <v>229</v>
       </c>
@@ -7513,13 +8194,13 @@
       </c>
     </row>
     <row r="249" spans="1:4" ht="16" customHeight="1">
-      <c r="A249" s="23"/>
+      <c r="A249" s="40"/>
       <c r="B249" s="4" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="250" spans="1:4" ht="16" customHeight="1">
-      <c r="A250" s="23"/>
+      <c r="A250" s="40"/>
       <c r="B250" s="4" t="s">
         <v>231</v>
       </c>
@@ -7552,11 +8233,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A204:A210"/>
-    <mergeCell ref="A211:A222"/>
-    <mergeCell ref="A223:A231"/>
-    <mergeCell ref="A232:A240"/>
-    <mergeCell ref="A241:A250"/>
     <mergeCell ref="A192:A203"/>
     <mergeCell ref="A2:A34"/>
     <mergeCell ref="A35:A48"/>
@@ -7569,6 +8245,11 @@
     <mergeCell ref="A154:A169"/>
     <mergeCell ref="A170:A181"/>
     <mergeCell ref="A182:A191"/>
+    <mergeCell ref="A204:A210"/>
+    <mergeCell ref="A211:A222"/>
+    <mergeCell ref="A223:A231"/>
+    <mergeCell ref="A232:A240"/>
+    <mergeCell ref="A241:A250"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
